--- a/public/demo/careflow-district-demo.xlsx
+++ b/public/demo/careflow-district-demo.xlsx
@@ -903,7 +903,7 @@
         <x:v>district-01</x:v>
       </x:c>
       <x:c r="B11" s="12" t="str">
-        <x:v>晴里樓（合成）</x:v>
+        <x:v>晴里樓</x:v>
       </x:c>
       <x:c r="C11" s="12" t="str">
         <x:v>演示街區 01 號 · 虛構地址</x:v>
@@ -941,7 +941,7 @@
         <x:v>district-02</x:v>
       </x:c>
       <x:c r="B12" s="13" t="str">
-        <x:v>青禾樓（合成）</x:v>
+        <x:v>青禾樓</x:v>
       </x:c>
       <x:c r="C12" s="13" t="str">
         <x:v>演示街區 02 號 · 虛構地址</x:v>
@@ -976,7 +976,7 @@
         <x:v>district-03</x:v>
       </x:c>
       <x:c r="B13" s="12" t="str">
-        <x:v>映榕樓（合成）</x:v>
+        <x:v>映榕樓</x:v>
       </x:c>
       <x:c r="C13" s="12" t="str">
         <x:v>演示街區 03 號 · 虛構地址</x:v>
@@ -1016,7 +1016,7 @@
         <x:v>district-04</x:v>
       </x:c>
       <x:c r="B14" s="13" t="str">
-        <x:v>小滿樓（合成）</x:v>
+        <x:v>小滿樓</x:v>
       </x:c>
       <x:c r="C14" s="13" t="str">
         <x:v>演示街區 04 號 · 虛構地址</x:v>
@@ -1049,7 +1049,7 @@
         <x:v>district-05</x:v>
       </x:c>
       <x:c r="B15" s="12" t="str">
-        <x:v>常悅樓（合成）</x:v>
+        <x:v>常悅樓</x:v>
       </x:c>
       <x:c r="C15" s="12" t="str">
         <x:v>演示街區 05 號 · 虛構地址</x:v>
@@ -1086,7 +1086,7 @@
         <x:v>district-06</x:v>
       </x:c>
       <x:c r="B16" s="13" t="str">
-        <x:v>知秋樓（合成）</x:v>
+        <x:v>知秋樓</x:v>
       </x:c>
       <x:c r="C16" s="13" t="str">
         <x:v>演示街區 06 號 · 虛構地址</x:v>
@@ -1115,7 +1115,7 @@
         <x:v>district-07</x:v>
       </x:c>
       <x:c r="B17" s="12" t="str">
-        <x:v>晴川樓（合成）</x:v>
+        <x:v>晴川樓</x:v>
       </x:c>
       <x:c r="C17" s="12" t="str">
         <x:v>演示街區 07 號 · 虛構地址</x:v>
@@ -1157,7 +1157,7 @@
         <x:v>district-08</x:v>
       </x:c>
       <x:c r="B18" s="13" t="str">
-        <x:v>穗安樓（合成）</x:v>
+        <x:v>穗安樓</x:v>
       </x:c>
       <x:c r="C18" s="13" t="str">
         <x:v>演示街區 08 號 · 虛構地址</x:v>
@@ -1191,7 +1191,7 @@
         <x:v>district-09</x:v>
       </x:c>
       <x:c r="B19" s="12" t="str">
-        <x:v>棠和樓（合成）</x:v>
+        <x:v>棠和樓</x:v>
       </x:c>
       <x:c r="C19" s="12" t="str">
         <x:v>演示街區 09 號 · 虛構地址</x:v>
@@ -1227,7 +1227,7 @@
         <x:v>district-10</x:v>
       </x:c>
       <x:c r="B20" s="13" t="str">
-        <x:v>日和樓（合成）</x:v>
+        <x:v>日和樓</x:v>
       </x:c>
       <x:c r="C20" s="13" t="str">
         <x:v>演示街區 10 號 · 虛構地址</x:v>
@@ -1259,7 +1259,7 @@
         <x:v>district-11</x:v>
       </x:c>
       <x:c r="B21" s="12" t="str">
-        <x:v>朗月樓（合成）</x:v>
+        <x:v>朗月樓</x:v>
       </x:c>
       <x:c r="C21" s="12" t="str">
         <x:v>演示街區 11 號 · 虛構地址</x:v>
@@ -1298,7 +1298,7 @@
         <x:v>district-12</x:v>
       </x:c>
       <x:c r="B22" s="13" t="str">
-        <x:v>杏林樓（合成）</x:v>
+        <x:v>杏林樓</x:v>
       </x:c>
       <x:c r="C22" s="13" t="str">
         <x:v>演示街區 12 號 · 虛構地址</x:v>
@@ -1327,7 +1327,7 @@
         <x:v>district-13</x:v>
       </x:c>
       <x:c r="B23" s="12" t="str">
-        <x:v>拾光樓（合成）</x:v>
+        <x:v>拾光樓</x:v>
       </x:c>
       <x:c r="C23" s="12" t="str">
         <x:v>演示街區 13 號 · 虛構地址</x:v>
@@ -1368,7 +1368,7 @@
         <x:v>district-14</x:v>
       </x:c>
       <x:c r="B24" s="13" t="str">
-        <x:v>和煦樓（合成）</x:v>
+        <x:v>和煦樓</x:v>
       </x:c>
       <x:c r="C24" s="13" t="str">
         <x:v>演示街區 14 號 · 虛構地址</x:v>
@@ -1400,7 +1400,7 @@
         <x:v>district-15</x:v>
       </x:c>
       <x:c r="B25" s="12" t="str">
-        <x:v>榕溪樓（合成）</x:v>
+        <x:v>榕溪樓</x:v>
       </x:c>
       <x:c r="C25" s="12" t="str">
         <x:v>演示街區 15 號 · 虛構地址</x:v>
@@ -1436,7 +1436,7 @@
         <x:v>district-16</x:v>
       </x:c>
       <x:c r="B26" s="13" t="str">
-        <x:v>微光樓（合成）</x:v>
+        <x:v>微光樓</x:v>
       </x:c>
       <x:c r="C26" s="13" t="str">
         <x:v>演示街區 16 號 · 虛構地址</x:v>
@@ -1594,7 +1594,7 @@
       </x:c>
       <x:c r="C9" s="18" t="str"/>
       <x:c r="D9" s="12" t="str">
-        <x:v>晴里樓（合成） · 1樓 A室（合成）</x:v>
+        <x:v>晴里樓 · 1樓 A室（合成）</x:v>
       </x:c>
       <x:c r="E9" s="12" t="str">
         <x:v>合成：演示名冊記錄，不含真實姓名、電話或個人資料。</x:v>
@@ -1615,7 +1615,7 @@
       </x:c>
       <x:c r="C10" s="19" t="str"/>
       <x:c r="D10" s="13" t="str">
-        <x:v>晴里樓（合成） · 1樓 A室（合成）</x:v>
+        <x:v>晴里樓 · 1樓 A室（合成）</x:v>
       </x:c>
       <x:c r="E10" s="13" t="str">
         <x:v>合成：演示名冊記錄，不含真實姓名、電話或個人資料。</x:v>
@@ -1636,7 +1636,7 @@
       </x:c>
       <x:c r="C11" s="18" t="str"/>
       <x:c r="D11" s="12" t="str">
-        <x:v>晴里樓（合成） · 1樓 C室（合成）</x:v>
+        <x:v>晴里樓 · 1樓 C室（合成）</x:v>
       </x:c>
       <x:c r="E11" s="12" t="str">
         <x:v>合成：只保留稱呼，未提供電話；聯絡意願待確認。</x:v>
@@ -1657,7 +1657,7 @@
       </x:c>
       <x:c r="C12" s="19" t="str"/>
       <x:c r="D12" s="13" t="str">
-        <x:v>晴里樓（合成） · 2樓 B室（合成）</x:v>
+        <x:v>晴里樓 · 2樓 B室（合成）</x:v>
       </x:c>
       <x:c r="E12" s="13" t="str">
         <x:v>合成：演示名冊記錄，不含真實姓名、電話或個人資料。</x:v>
@@ -1678,7 +1678,7 @@
       </x:c>
       <x:c r="C13" s="18" t="str"/>
       <x:c r="D13" s="12" t="str">
-        <x:v>青禾樓（合成） · 1樓 A室（合成）</x:v>
+        <x:v>青禾樓 · 1樓 A室（合成）</x:v>
       </x:c>
       <x:c r="E13" s="12" t="str">
         <x:v>合成：演示名冊記錄，不含真實姓名、電話或個人資料。</x:v>
@@ -1699,7 +1699,7 @@
       </x:c>
       <x:c r="C14" s="19" t="str"/>
       <x:c r="D14" s="13" t="str">
-        <x:v>青禾樓（合成） · 1樓 A室（合成）</x:v>
+        <x:v>青禾樓 · 1樓 A室（合成）</x:v>
       </x:c>
       <x:c r="E14" s="13" t="str">
         <x:v>合成：演示名冊記錄，不含真實姓名、電話或個人資料。</x:v>
@@ -1720,7 +1720,7 @@
       </x:c>
       <x:c r="C15" s="18" t="str"/>
       <x:c r="D15" s="12" t="str">
-        <x:v>青禾樓（合成） · 1樓 C室（合成）</x:v>
+        <x:v>青禾樓 · 1樓 C室（合成）</x:v>
       </x:c>
       <x:c r="E15" s="12" t="str">
         <x:v>合成：只保留稱呼，未提供電話；聯絡意願待確認。</x:v>
@@ -1741,7 +1741,7 @@
       </x:c>
       <x:c r="C16" s="19" t="str"/>
       <x:c r="D16" s="13" t="str">
-        <x:v>青禾樓（合成） · 2樓 A室（合成）</x:v>
+        <x:v>青禾樓 · 2樓 A室（合成）</x:v>
       </x:c>
       <x:c r="E16" s="13" t="str">
         <x:v>合成：演示名冊記錄，不含真實姓名、電話或個人資料。</x:v>
@@ -1762,7 +1762,7 @@
       </x:c>
       <x:c r="C17" s="18" t="str"/>
       <x:c r="D17" s="12" t="str">
-        <x:v>映榕樓（合成） · 1樓 A室（合成）</x:v>
+        <x:v>映榕樓 · 1樓 A室（合成）</x:v>
       </x:c>
       <x:c r="E17" s="12" t="str">
         <x:v>合成：演示名冊記錄，不含真實姓名、電話或個人資料。</x:v>
@@ -1783,7 +1783,7 @@
       </x:c>
       <x:c r="C18" s="19" t="str"/>
       <x:c r="D18" s="13" t="str">
-        <x:v>映榕樓（合成） · 1樓 A室（合成）</x:v>
+        <x:v>映榕樓 · 1樓 A室（合成）</x:v>
       </x:c>
       <x:c r="E18" s="13" t="str">
         <x:v>合成：演示名冊記錄，不含真實姓名、電話或個人資料。</x:v>
@@ -1804,7 +1804,7 @@
       </x:c>
       <x:c r="C19" s="18" t="str"/>
       <x:c r="D19" s="12" t="str">
-        <x:v>映榕樓（合成） · 2樓 A室（合成）</x:v>
+        <x:v>映榕樓 · 2樓 A室（合成）</x:v>
       </x:c>
       <x:c r="E19" s="12" t="str">
         <x:v>合成：只保留稱呼，未提供電話；聯絡意願待確認。</x:v>
@@ -1825,7 +1825,7 @@
       </x:c>
       <x:c r="C20" s="19" t="str"/>
       <x:c r="D20" s="13" t="str">
-        <x:v>映榕樓（合成） · 3樓 A室（合成）</x:v>
+        <x:v>映榕樓 · 3樓 A室（合成）</x:v>
       </x:c>
       <x:c r="E20" s="13" t="str">
         <x:v>合成：演示名冊記錄，不含真實姓名、電話或個人資料。</x:v>
@@ -1846,7 +1846,7 @@
       </x:c>
       <x:c r="C21" s="18" t="str"/>
       <x:c r="D21" s="12" t="str">
-        <x:v>小滿樓（合成） · 1樓 A室（合成）</x:v>
+        <x:v>小滿樓 · 1樓 A室（合成）</x:v>
       </x:c>
       <x:c r="E21" s="12" t="str">
         <x:v>合成：演示名冊記錄，不含真實姓名、電話或個人資料。</x:v>
@@ -1867,7 +1867,7 @@
       </x:c>
       <x:c r="C22" s="19" t="str"/>
       <x:c r="D22" s="13" t="str">
-        <x:v>小滿樓（合成） · 1樓 A室（合成）</x:v>
+        <x:v>小滿樓 · 1樓 A室（合成）</x:v>
       </x:c>
       <x:c r="E22" s="13" t="str">
         <x:v>合成：演示名冊記錄，不含真實姓名、電話或個人資料。</x:v>
@@ -1888,7 +1888,7 @@
       </x:c>
       <x:c r="C23" s="18" t="str"/>
       <x:c r="D23" s="12" t="str">
-        <x:v>小滿樓（合成） · 1樓 C室（合成）</x:v>
+        <x:v>小滿樓 · 1樓 C室（合成）</x:v>
       </x:c>
       <x:c r="E23" s="12" t="str">
         <x:v>合成：只保留稱呼，未提供電話；聯絡意願待確認。</x:v>
@@ -1909,7 +1909,7 @@
       </x:c>
       <x:c r="C24" s="19" t="str"/>
       <x:c r="D24" s="13" t="str">
-        <x:v>小滿樓（合成） · 2樓 B室（合成）</x:v>
+        <x:v>小滿樓 · 2樓 B室（合成）</x:v>
       </x:c>
       <x:c r="E24" s="13" t="str">
         <x:v>合成：演示名冊記錄，不含真實姓名、電話或個人資料。</x:v>
@@ -1930,7 +1930,7 @@
       </x:c>
       <x:c r="C25" s="18" t="str"/>
       <x:c r="D25" s="12" t="str">
-        <x:v>常悅樓（合成） · 1樓 A室（合成）</x:v>
+        <x:v>常悅樓 · 1樓 A室（合成）</x:v>
       </x:c>
       <x:c r="E25" s="12" t="str">
         <x:v>合成：演示名冊記錄，不含真實姓名、電話或個人資料。</x:v>
@@ -1951,7 +1951,7 @@
       </x:c>
       <x:c r="C26" s="19" t="str"/>
       <x:c r="D26" s="13" t="str">
-        <x:v>常悅樓（合成） · 1樓 A室（合成）</x:v>
+        <x:v>常悅樓 · 1樓 A室（合成）</x:v>
       </x:c>
       <x:c r="E26" s="13" t="str">
         <x:v>合成：演示名冊記錄，不含真實姓名、電話或個人資料。</x:v>
@@ -1972,7 +1972,7 @@
       </x:c>
       <x:c r="C27" s="18" t="str"/>
       <x:c r="D27" s="12" t="str">
-        <x:v>常悅樓（合成） · 1樓 C室（合成）</x:v>
+        <x:v>常悅樓 · 1樓 C室（合成）</x:v>
       </x:c>
       <x:c r="E27" s="12" t="str">
         <x:v>合成：只保留稱呼，未提供電話；聯絡意願待確認。</x:v>
@@ -1993,7 +1993,7 @@
       </x:c>
       <x:c r="C28" s="19" t="str"/>
       <x:c r="D28" s="13" t="str">
-        <x:v>常悅樓（合成） · 2樓 A室（合成）</x:v>
+        <x:v>常悅樓 · 2樓 A室（合成）</x:v>
       </x:c>
       <x:c r="E28" s="13" t="str">
         <x:v>合成：演示名冊記錄，不含真實姓名、電話或個人資料。</x:v>
@@ -2014,7 +2014,7 @@
       </x:c>
       <x:c r="C29" s="18" t="str"/>
       <x:c r="D29" s="12" t="str">
-        <x:v>知秋樓（合成） · 具體位置待核對（合成）</x:v>
+        <x:v>知秋樓 · 具體位置待核對（合成）</x:v>
       </x:c>
       <x:c r="E29" s="12" t="str">
         <x:v>合成：演示名冊記錄，不含真實姓名、電話或個人資料。</x:v>
@@ -2035,7 +2035,7 @@
       </x:c>
       <x:c r="C30" s="19" t="str"/>
       <x:c r="D30" s="13" t="str">
-        <x:v>知秋樓（合成） · 具體位置待核對（合成）</x:v>
+        <x:v>知秋樓 · 具體位置待核對（合成）</x:v>
       </x:c>
       <x:c r="E30" s="13" t="str">
         <x:v>合成：演示名冊記錄，不含真實姓名、電話或個人資料。</x:v>
@@ -2056,7 +2056,7 @@
       </x:c>
       <x:c r="C31" s="18" t="str"/>
       <x:c r="D31" s="12" t="str">
-        <x:v>知秋樓（合成） · 具體位置待核對（合成）</x:v>
+        <x:v>知秋樓 · 具體位置待核對（合成）</x:v>
       </x:c>
       <x:c r="E31" s="12" t="str">
         <x:v>合成：只保留稱呼，未提供電話；聯絡意願待確認。</x:v>
@@ -2077,7 +2077,7 @@
       </x:c>
       <x:c r="C32" s="19" t="str"/>
       <x:c r="D32" s="13" t="str">
-        <x:v>晴川樓（合成） · 1樓 A室（合成）</x:v>
+        <x:v>晴川樓 · 1樓 A室（合成）</x:v>
       </x:c>
       <x:c r="E32" s="13" t="str">
         <x:v>合成：演示名冊記錄，不含真實姓名、電話或個人資料。</x:v>
@@ -2098,7 +2098,7 @@
       </x:c>
       <x:c r="C33" s="18" t="str"/>
       <x:c r="D33" s="12" t="str">
-        <x:v>晴川樓（合成） · 1樓 A室（合成）</x:v>
+        <x:v>晴川樓 · 1樓 A室（合成）</x:v>
       </x:c>
       <x:c r="E33" s="12" t="str">
         <x:v>合成：演示名冊記錄，不含真實姓名、電話或個人資料。</x:v>
@@ -2119,7 +2119,7 @@
       </x:c>
       <x:c r="C34" s="19" t="str"/>
       <x:c r="D34" s="13" t="str">
-        <x:v>晴川樓（合成） · 2樓 A室（合成）</x:v>
+        <x:v>晴川樓 · 2樓 A室（合成）</x:v>
       </x:c>
       <x:c r="E34" s="13" t="str">
         <x:v>合成：只保留稱呼，未提供電話；聯絡意願待確認。</x:v>
@@ -2140,7 +2140,7 @@
       </x:c>
       <x:c r="C35" s="18" t="str"/>
       <x:c r="D35" s="12" t="str">
-        <x:v>晴川樓（合成） · 3樓 A室（合成）</x:v>
+        <x:v>晴川樓 · 3樓 A室（合成）</x:v>
       </x:c>
       <x:c r="E35" s="12" t="str">
         <x:v>合成：演示名冊記錄，不含真實姓名、電話或個人資料。</x:v>
@@ -2161,7 +2161,7 @@
       </x:c>
       <x:c r="C36" s="19" t="str"/>
       <x:c r="D36" s="13" t="str">
-        <x:v>穗安樓（合成） · 1樓 A室（合成）</x:v>
+        <x:v>穗安樓 · 1樓 A室（合成）</x:v>
       </x:c>
       <x:c r="E36" s="13" t="str">
         <x:v>合成：演示名冊記錄，不含真實姓名、電話或個人資料。</x:v>
@@ -2182,7 +2182,7 @@
       </x:c>
       <x:c r="C37" s="18" t="str"/>
       <x:c r="D37" s="12" t="str">
-        <x:v>穗安樓（合成） · 1樓 A室（合成）</x:v>
+        <x:v>穗安樓 · 1樓 A室（合成）</x:v>
       </x:c>
       <x:c r="E37" s="12" t="str">
         <x:v>合成：演示名冊記錄，不含真實姓名、電話或個人資料。</x:v>
@@ -2203,7 +2203,7 @@
       </x:c>
       <x:c r="C38" s="19" t="str"/>
       <x:c r="D38" s="13" t="str">
-        <x:v>穗安樓（合成） · 1樓 C室（合成）</x:v>
+        <x:v>穗安樓 · 1樓 C室（合成）</x:v>
       </x:c>
       <x:c r="E38" s="13" t="str">
         <x:v>合成：只保留稱呼，未提供電話；聯絡意願待確認。</x:v>
@@ -2224,7 +2224,7 @@
       </x:c>
       <x:c r="C39" s="18" t="str"/>
       <x:c r="D39" s="12" t="str">
-        <x:v>穗安樓（合成） · 2樓 B室（合成）</x:v>
+        <x:v>穗安樓 · 2樓 B室（合成）</x:v>
       </x:c>
       <x:c r="E39" s="12" t="str">
         <x:v>合成：演示名冊記錄，不含真實姓名、電話或個人資料。</x:v>
@@ -2245,7 +2245,7 @@
       </x:c>
       <x:c r="C40" s="19" t="str"/>
       <x:c r="D40" s="13" t="str">
-        <x:v>棠和樓（合成） · 1樓 A室（合成）</x:v>
+        <x:v>棠和樓 · 1樓 A室（合成）</x:v>
       </x:c>
       <x:c r="E40" s="13" t="str">
         <x:v>合成：演示名冊記錄，不含真實姓名、電話或個人資料。</x:v>
@@ -2266,7 +2266,7 @@
       </x:c>
       <x:c r="C41" s="18" t="str"/>
       <x:c r="D41" s="12" t="str">
-        <x:v>棠和樓（合成） · 1樓 A室（合成）</x:v>
+        <x:v>棠和樓 · 1樓 A室（合成）</x:v>
       </x:c>
       <x:c r="E41" s="12" t="str">
         <x:v>合成：演示名冊記錄，不含真實姓名、電話或個人資料。</x:v>
@@ -2287,7 +2287,7 @@
       </x:c>
       <x:c r="C42" s="19" t="str"/>
       <x:c r="D42" s="13" t="str">
-        <x:v>棠和樓（合成） · 1樓 C室（合成）</x:v>
+        <x:v>棠和樓 · 1樓 C室（合成）</x:v>
       </x:c>
       <x:c r="E42" s="13" t="str">
         <x:v>合成：只保留稱呼，未提供電話；聯絡意願待確認。</x:v>
@@ -2308,7 +2308,7 @@
       </x:c>
       <x:c r="C43" s="18" t="str"/>
       <x:c r="D43" s="12" t="str">
-        <x:v>棠和樓（合成） · 2樓 A室（合成）</x:v>
+        <x:v>棠和樓 · 2樓 A室（合成）</x:v>
       </x:c>
       <x:c r="E43" s="12" t="str">
         <x:v>合成：演示名冊記錄，不含真實姓名、電話或個人資料。</x:v>
@@ -2329,7 +2329,7 @@
       </x:c>
       <x:c r="C44" s="19" t="str"/>
       <x:c r="D44" s="13" t="str">
-        <x:v>日和樓（合成） · 1樓 A室（合成）</x:v>
+        <x:v>日和樓 · 1樓 A室（合成）</x:v>
       </x:c>
       <x:c r="E44" s="13" t="str">
         <x:v>合成：演示名冊記錄，不含真實姓名、電話或個人資料。</x:v>
@@ -2350,7 +2350,7 @@
       </x:c>
       <x:c r="C45" s="18" t="str"/>
       <x:c r="D45" s="12" t="str">
-        <x:v>日和樓（合成） · 1樓 A室（合成）</x:v>
+        <x:v>日和樓 · 1樓 A室（合成）</x:v>
       </x:c>
       <x:c r="E45" s="12" t="str">
         <x:v>合成：演示名冊記錄，不含真實姓名、電話或個人資料。</x:v>
@@ -2371,7 +2371,7 @@
       </x:c>
       <x:c r="C46" s="19" t="str"/>
       <x:c r="D46" s="13" t="str">
-        <x:v>日和樓（合成） · 2樓 A室（合成）</x:v>
+        <x:v>日和樓 · 2樓 A室（合成）</x:v>
       </x:c>
       <x:c r="E46" s="13" t="str">
         <x:v>合成：只保留稱呼，未提供電話；聯絡意願待確認。</x:v>
@@ -2392,7 +2392,7 @@
       </x:c>
       <x:c r="C47" s="18" t="str"/>
       <x:c r="D47" s="12" t="str">
-        <x:v>日和樓（合成） · 3樓 A室（合成）</x:v>
+        <x:v>日和樓 · 3樓 A室（合成）</x:v>
       </x:c>
       <x:c r="E47" s="12" t="str">
         <x:v>合成：演示名冊記錄，不含真實姓名、電話或個人資料。</x:v>
@@ -2413,7 +2413,7 @@
       </x:c>
       <x:c r="C48" s="19" t="str"/>
       <x:c r="D48" s="13" t="str">
-        <x:v>朗月樓（合成） · 1樓 A室（合成）</x:v>
+        <x:v>朗月樓 · 1樓 A室（合成）</x:v>
       </x:c>
       <x:c r="E48" s="13" t="str">
         <x:v>合成：演示名冊記錄，不含真實姓名、電話或個人資料。</x:v>
@@ -2434,7 +2434,7 @@
       </x:c>
       <x:c r="C49" s="18" t="str"/>
       <x:c r="D49" s="12" t="str">
-        <x:v>朗月樓（合成） · 1樓 A室（合成）</x:v>
+        <x:v>朗月樓 · 1樓 A室（合成）</x:v>
       </x:c>
       <x:c r="E49" s="12" t="str">
         <x:v>合成：演示名冊記錄，不含真實姓名、電話或個人資料。</x:v>
@@ -2455,7 +2455,7 @@
       </x:c>
       <x:c r="C50" s="19" t="str"/>
       <x:c r="D50" s="13" t="str">
-        <x:v>朗月樓（合成） · 1樓 C室（合成）</x:v>
+        <x:v>朗月樓 · 1樓 C室（合成）</x:v>
       </x:c>
       <x:c r="E50" s="13" t="str">
         <x:v>合成：只保留稱呼，未提供電話；聯絡意願待確認。</x:v>
@@ -2476,7 +2476,7 @@
       </x:c>
       <x:c r="C51" s="18" t="str"/>
       <x:c r="D51" s="12" t="str">
-        <x:v>朗月樓（合成） · 2樓 B室（合成）</x:v>
+        <x:v>朗月樓 · 2樓 B室（合成）</x:v>
       </x:c>
       <x:c r="E51" s="12" t="str">
         <x:v>合成：演示名冊記錄，不含真實姓名、電話或個人資料。</x:v>
@@ -2497,7 +2497,7 @@
       </x:c>
       <x:c r="C52" s="19" t="str"/>
       <x:c r="D52" s="13" t="str">
-        <x:v>杏林樓（合成） · 具體位置待核對（合成）</x:v>
+        <x:v>杏林樓 · 具體位置待核對（合成）</x:v>
       </x:c>
       <x:c r="E52" s="13" t="str">
         <x:v>合成：演示名冊記錄，不含真實姓名、電話或個人資料。</x:v>
@@ -2518,7 +2518,7 @@
       </x:c>
       <x:c r="C53" s="18" t="str"/>
       <x:c r="D53" s="12" t="str">
-        <x:v>杏林樓（合成） · 具體位置待核對（合成）</x:v>
+        <x:v>杏林樓 · 具體位置待核對（合成）</x:v>
       </x:c>
       <x:c r="E53" s="12" t="str">
         <x:v>合成：演示名冊記錄，不含真實姓名、電話或個人資料。</x:v>
@@ -2539,7 +2539,7 @@
       </x:c>
       <x:c r="C54" s="19" t="str"/>
       <x:c r="D54" s="13" t="str">
-        <x:v>杏林樓（合成） · 具體位置待核對（合成）</x:v>
+        <x:v>杏林樓 · 具體位置待核對（合成）</x:v>
       </x:c>
       <x:c r="E54" s="13" t="str">
         <x:v>合成：只保留稱呼，未提供電話；聯絡意願待確認。</x:v>
@@ -2560,7 +2560,7 @@
       </x:c>
       <x:c r="C55" s="18" t="str"/>
       <x:c r="D55" s="12" t="str">
-        <x:v>拾光樓（合成） · 1樓 A室（合成）</x:v>
+        <x:v>拾光樓 · 1樓 A室（合成）</x:v>
       </x:c>
       <x:c r="E55" s="12" t="str">
         <x:v>合成：演示名冊記錄，不含真實姓名、電話或個人資料。</x:v>
@@ -2581,7 +2581,7 @@
       </x:c>
       <x:c r="C56" s="19" t="str"/>
       <x:c r="D56" s="13" t="str">
-        <x:v>拾光樓（合成） · 1樓 A室（合成）</x:v>
+        <x:v>拾光樓 · 1樓 A室（合成）</x:v>
       </x:c>
       <x:c r="E56" s="13" t="str">
         <x:v>合成：演示名冊記錄，不含真實姓名、電話或個人資料。</x:v>
@@ -2602,7 +2602,7 @@
       </x:c>
       <x:c r="C57" s="18" t="str"/>
       <x:c r="D57" s="12" t="str">
-        <x:v>拾光樓（合成） · 2樓 A室（合成）</x:v>
+        <x:v>拾光樓 · 2樓 A室（合成）</x:v>
       </x:c>
       <x:c r="E57" s="12" t="str">
         <x:v>合成：只保留稱呼，未提供電話；聯絡意願待確認。</x:v>
@@ -2623,7 +2623,7 @@
       </x:c>
       <x:c r="C58" s="19" t="str"/>
       <x:c r="D58" s="13" t="str">
-        <x:v>拾光樓（合成） · 3樓 A室（合成）</x:v>
+        <x:v>拾光樓 · 3樓 A室（合成）</x:v>
       </x:c>
       <x:c r="E58" s="13" t="str">
         <x:v>合成：演示名冊記錄，不含真實姓名、電話或個人資料。</x:v>
@@ -2644,7 +2644,7 @@
       </x:c>
       <x:c r="C59" s="18" t="str"/>
       <x:c r="D59" s="12" t="str">
-        <x:v>榕溪樓（合成） · 1樓 A室（合成）</x:v>
+        <x:v>榕溪樓 · 1樓 A室（合成）</x:v>
       </x:c>
       <x:c r="E59" s="12" t="str">
         <x:v>合成：演示名冊記錄，不含真實姓名、電話或個人資料。</x:v>
@@ -2665,7 +2665,7 @@
       </x:c>
       <x:c r="C60" s="19" t="str"/>
       <x:c r="D60" s="13" t="str">
-        <x:v>榕溪樓（合成） · 1樓 A室（合成）</x:v>
+        <x:v>榕溪樓 · 1樓 A室（合成）</x:v>
       </x:c>
       <x:c r="E60" s="13" t="str">
         <x:v>合成：演示名冊記錄，不含真實姓名、電話或個人資料。</x:v>
@@ -2686,7 +2686,7 @@
       </x:c>
       <x:c r="C61" s="18" t="str"/>
       <x:c r="D61" s="12" t="str">
-        <x:v>榕溪樓（合成） · 1樓 C室（合成）</x:v>
+        <x:v>榕溪樓 · 1樓 C室（合成）</x:v>
       </x:c>
       <x:c r="E61" s="12" t="str">
         <x:v>合成：只保留稱呼，未提供電話；聯絡意願待確認。</x:v>
@@ -2707,7 +2707,7 @@
       </x:c>
       <x:c r="C62" s="19" t="str"/>
       <x:c r="D62" s="13" t="str">
-        <x:v>榕溪樓（合成） · 2樓 B室（合成）</x:v>
+        <x:v>榕溪樓 · 2樓 B室（合成）</x:v>
       </x:c>
       <x:c r="E62" s="13" t="str">
         <x:v>合成：演示名冊記錄，不含真實姓名、電話或個人資料。</x:v>
@@ -18929,7 +18929,7 @@
         <x:v>district-01-r3-1</x:v>
       </x:c>
       <x:c r="B12" s="11" t="str">
-        <x:v>晴里樓（合成）</x:v>
+        <x:v>晴里樓</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
         <x:v>1樓 A室</x:v>
@@ -18955,7 +18955,7 @@
         <x:v>district-03-r3-1</x:v>
       </x:c>
       <x:c r="B13" s="10" t="str">
-        <x:v>映榕樓（合成）</x:v>
+        <x:v>映榕樓</x:v>
       </x:c>
       <x:c r="C13" s="10" t="str">
         <x:v>1樓 A室</x:v>
@@ -18979,7 +18979,7 @@
         <x:v>district-04-r3-1</x:v>
       </x:c>
       <x:c r="B14" s="11" t="str">
-        <x:v>小滿樓（合成）</x:v>
+        <x:v>小滿樓</x:v>
       </x:c>
       <x:c r="C14" s="11" t="str">
         <x:v>1樓 A室</x:v>
@@ -19003,7 +19003,7 @@
         <x:v>district-06-r3-1</x:v>
       </x:c>
       <x:c r="B15" s="10" t="str">
-        <x:v>知秋樓（合成）</x:v>
+        <x:v>知秋樓</x:v>
       </x:c>
       <x:c r="C15" s="10" t="str">
         <x:v>大廈層面</x:v>
@@ -19027,7 +19027,7 @@
         <x:v>district-07-r3-1</x:v>
       </x:c>
       <x:c r="B16" s="11" t="str">
-        <x:v>晴川樓（合成）</x:v>
+        <x:v>晴川樓</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
         <x:v>1樓 A室</x:v>
@@ -19051,7 +19051,7 @@
         <x:v>district-09-r3-1</x:v>
       </x:c>
       <x:c r="B17" s="10" t="str">
-        <x:v>棠和樓（合成）</x:v>
+        <x:v>棠和樓</x:v>
       </x:c>
       <x:c r="C17" s="10" t="str">
         <x:v>1樓 A室</x:v>
@@ -19075,7 +19075,7 @@
         <x:v>district-10-r3-1</x:v>
       </x:c>
       <x:c r="B18" s="11" t="str">
-        <x:v>日和樓（合成）</x:v>
+        <x:v>日和樓</x:v>
       </x:c>
       <x:c r="C18" s="11" t="str">
         <x:v>1樓 A室</x:v>
@@ -19099,7 +19099,7 @@
         <x:v>district-12-r3-1</x:v>
       </x:c>
       <x:c r="B19" s="10" t="str">
-        <x:v>杏林樓（合成）</x:v>
+        <x:v>杏林樓</x:v>
       </x:c>
       <x:c r="C19" s="10" t="str">
         <x:v>大廈層面</x:v>
@@ -19123,7 +19123,7 @@
         <x:v>district-13-r3-1</x:v>
       </x:c>
       <x:c r="B20" s="11" t="str">
-        <x:v>拾光樓（合成）</x:v>
+        <x:v>拾光樓</x:v>
       </x:c>
       <x:c r="C20" s="11" t="str">
         <x:v>1樓 A室</x:v>
@@ -19147,7 +19147,7 @@
         <x:v>district-15-r3-1</x:v>
       </x:c>
       <x:c r="B21" s="10" t="str">
-        <x:v>榕溪樓（合成）</x:v>
+        <x:v>榕溪樓</x:v>
       </x:c>
       <x:c r="C21" s="10" t="str">
         <x:v>1樓 A室</x:v>
@@ -19221,7 +19221,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B7" s="37" t="str">
-        <x:v>{"schemaVersion":"0.1-demo","isSynthetic":true,"notice":"全區合成演示：20 個大廈位置用作介面測試；樓名、地址、樓層、單位、住戶及記錄均屬虛構，不代表地圖底圖中的真實建築或居民。依原紙本＋Excel 工作流設計，欄位仍待機構確認。","buildings":[{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an","name":"裕安樓","address":"西營盤示範街 1 號（合成）","layoutDeclared":true,"floorCount":8,"initialCoverage":"UNVISITED","coordinates":{"lng":114.14178818464279,"lat":22.286363930711317},"footprint":[[114.14168894290924,22.286500432351488],[114.1418981552124,22.286495468660235],[114.14189279079437,22.286227429071147],[114.14167821407318,22.286237356472498],[114.14168894290924,22.286500432351488]]},{"isSynthetic":true,"provisional":true,"id":"bldg-hoi-king","name":"海景樓","address":"西營盤示範街 8 號（合成）","layoutDeclared":true,"floorCount":2,"initialCoverage":"UNVISITED","coordinates":{"lng":114.14255797863007,"lat":22.28661211534631},"footprint":[[114.14262235164642,22.286664234063778],[114.14262235164642,22.286619560888553],[114.14259016513824,22.286624524575387],[114.14258480072021,22.286589778763798],[114.14263308048248,22.286589778763798],[114.14263308048248,22.286555032943582],[114.14248287677765,22.286559996632704],[114.14248287677765,22.28659474245171],[114.14253115653992,22.28659474245171],[114.14253115653992,22.286624524575387],[114.14249897003174,22.286624524575387],[114.14249897003174,22.286669197749035],[114.14262235164642,22.286664234063778]]},{"isSynthetic":true,"provisional":true,"id":"bldg-duk-cheong","name":"德昌樓","address":"西營盤示範街 16 號（合成）","layoutDeclared":false,"initialCoverage":"UNKNOWN","coordinates":{"lng":114.14136976003647,"lat":22.286808180844794},"footprint":[[114.1414475440979,22.286733725641312],[114.14129197597504,22.286733725641312],[114.14129197597504,22.286882636048276],[114.1414475440979,22.286877672370593],[114.1414475440979,22.286733725641312]]},{"isSynthetic":true,"provisional":true,"id":"bldg-on-wo","name":"安和樓","address":"西營盤示範街 24 號（合成）","layoutDeclared":false,"initialCoverage":"UNKNOWN","coordinates":{"lng":114.14208590984344,"lat":22.28576580411479},"footprint":[[114.14213418960571,22.285825368723906],[114.14212882518768,22.28570127579063],[114.14203763008118,22.285706239510063],[114.1420429944992,22.285830332438948],[114.14213418960571,22.285825368723906]]},{"isSynthetic":true,"provisional":true,"id":"district-01","name":"晴里樓（合成）","address":"演示街區 01 號 · 虛構地址","coordinates":{"lng":114.13954049348831,"lat":22.287835658837054},"footprint":[[114.13945734500885,22.287890258967195],[114.13946807384491,22.287865440755937],[114.13947880268097,22.28787040439856],[114.13946270942688,22.287920040814882],[114.1395378112793,22.287939895376482],[114.13955390453339,22.287890258967195],[114.13956463336945,22.287890258967195],[114.13954854011536,22.287944859016434],[114.13962364196777,22.28796471357451],[114.13963973522186,22.287910113533016],[114.13965582847595,22.28791507717405],[114.13966655731201,22.28787536804097],[114.13965046405792,22.28787040439856],[114.13966119289398,22.287835658896626],[114.1396826505661,22.287840622540287],[114.13970410823822,22.28778105880474],[114.13943588733673,22.287706604099597],[114.1393768787384,22.28789522260891],[114.13945198059082,22.28791507717405],[114.13945734500885,22.287890258967195]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":10},{"isSynthetic":true,"provisional":true,"id":"district-02","name":"青禾樓（合成）","address":"演示街區 02 號 · 虛構地址","coordinates":{"lng":114.14060264825821,"lat":22.287644558357755},"footprint":[[114.14048731327057,22.28780091338608],[114.14061069488525,22.28783069525278],[114.14062678813934,22.28778105880474],[114.1406911611557,22.287795949740996],[114.14071798324585,22.287696676802582],[114.14065897464752,22.28768178585574],[114.14071261882782,22.28749316705843],[114.1405838727951,22.28745842146273],[114.14048731327057,22.28780091338608]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":7},{"isSynthetic":true,"provisional":true,"id":"district-03","name":"映榕樓（合成）","address":"演示街區 03 號 · 虛構地址","coordinates":{"lng":114.14200276136398,"lat":22.287753758732258},"footprint":[[114.14189279079437,22.287686749504857],[114.1418981552124,22.287825731608777],[114.1421127319336,22.28782076796459],[114.14210736751556,22.28768178585574],[114.14189279079437,22.287686749504857]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":12},{"isSynthetic":true,"provisional":true,"id":"district-04","name":"小滿樓（合成）","address":"演示街區 04 號 · 虛構地址","coordinates":{"lng":114.14324462413788,"lat":22.287714049553372},"footprint":[[114.14331436157227,22.28778105880474],[114.14330899715424,22.28764207665641],[114.14319097995758,22.287647040306936],[114.14319097995758,22.287751276927438],[114.14317488670349,22.287751276927438],[114.14317488670349,22.287786022450334],[114.14331436157227,22.28778105880474]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":5},{"isSynthetic":true,"provisional":true,"id":"district-05","name":"常悅樓（合成）","address":"演示街區 05 號 · 虛構地址","coordinates":{"lng":114.13936883211136,"lat":22.286842926596464},"footprint":[[114.13924276828766,22.28687270869274],[114.13945734500885,22.286927309139443],[114.13949489593506,22.286818108224736],[114.13928031921387,22.286758544053484],[114.13924276828766,22.28687270869274]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":9},{"isSynthetic":true,"provisional":true,"id":"district-06","name":"知秋樓（合成）","address":"演示街區 06 號 · 虛構地址","coordinates":{"lng":114.14092719554901,"lat":22.286840444772693},"footprint":[[114.14082527160645,22.28683796294284],[114.14087355136871,22.28683796294284],[114.14087355136871,22.2868925634031],[114.14098620414734,22.286887599725773],[114.14098620414734,22.28683299926358],[114.14102911949158,22.28683299926358],[114.14102911949158,22.286788326142286],[114.14082527160645,22.286793289823123],[114.14082527160645,22.28683796294284]],"layoutDeclared":false,"initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-07","name":"晴川樓（合成）","address":"演示街區 07 號 · 虛構地址","coordinates":{"lng":114.14216101169586,"lat":22.286723798239954},"footprint":[[114.14209127426147,22.286624524575387],[114.14209127426147,22.28665430669274],[114.14210200309753,22.28665430669274],[114.14210736751556,22.286793289823123],[114.1420966386795,22.286793289823123],[114.1420966386795,22.28682307190452],[114.14218246936798,22.28682307190452],[114.14217174053192,22.286763507735387],[114.14223074913025,22.286763507735387],[114.14223074913025,22.286674161434107],[114.14217174053192,22.286674161434107],[114.14217710494995,22.286624524575387],[114.14209127426147,22.286624524575387]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":14},{"isSynthetic":true,"provisional":true,"id":"district-08","name":"穗安樓（合成）","address":"演示街區 08 號 · 虛構地址","coordinates":{"lng":114.14348870515823,"lat":22.286728761932885},"footprint":[[114.14357721805573,22.286644379321004],[114.14339482784271,22.286649343006957],[114.14340019226074,22.286813144544766],[114.14358258247375,22.286808180864625],[114.14357721805573,22.286644379321004]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":6},{"isSynthetic":true,"provisional":true,"id":"district-09","name":"棠和樓（合成）","address":"演示街區 09 號 · 虛構地址","coordinates":{"lng":114.13955926895142,"lat":22.28589237884831},"footprint":[[114.13951098918915,22.28595442525767],[114.13961291313171,22.28594449783624],[114.13961291313171,22.28592960670275],[114.13965046405792,22.285924642991233],[114.13964509963989,22.285879969579653],[114.13960754871368,22.28588493329275],[114.13960218429565,22.285830332438948],[114.13955926895142,22.28583529615382],[114.13956463336945,22.285870042152922],[114.13954317569733,22.285870042152922],[114.13954317569733,22.28583529615382],[114.13950026035309,22.285840259868493],[114.13950562477112,22.285894860718443],[114.13946807384491,22.285894860718443],[114.13947343826294,22.285939534125234],[114.13951098918915,22.285939534125234],[114.13951098918915,22.28595442525767]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":8},{"isSynthetic":true,"provisional":true,"id":"district-10","name":"日和樓（合成）","address":"演示街區 10 號 · 虛構地址","coordinates":{"lng":114.14058923721313,"lat":22.285837777977676},"footprint":[[114.1406375169754,22.285899824431013],[114.14064824581146,22.285899824431013],[114.14064288139343,22.28576580412968],[114.1406375169754,22.28576580412968],[114.14063215255737,22.285740985541267],[114.14057850837708,22.285745949259294],[114.14057850837708,22.285775731563803],[114.14056777954102,22.285775731563803],[114.14056241512299,22.285800550146064],[114.14053022861481,22.285800550146064],[114.14053022861481,22.285855151011503],[114.1405463218689,22.285855151011503],[114.1405463218689,22.285875005866373],[114.14053022861481,22.285875005866373],[114.14053559303284,22.285924642991233],[114.14062142372131,22.285934570414085],[114.14062142372131,22.28592960670275],[114.1406375169754,22.28592960670275],[114.1406375169754,22.285899824431013]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":4},{"isSynthetic":true,"provisional":true,"id":"district-11","name":"朗月樓（合成）","address":"演示街區 11 號 · 虛構地址","coordinates":{"lng":114.14172112941742,"lat":22.285909751848486},"footprint":[[114.14187133312225,22.2858650784393],[114.14156556129456,22.285875005866373],[114.14156556129456,22.28595442525767],[114.14187669754028,22.28594449783624],[114.14187133312225,22.2858650784393]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":11},{"isSynthetic":true,"provisional":true,"id":"district-12","name":"杏林樓（合成）","address":"演示街區 12 號 · 虛構地址","coordinates":{"lng":114.14298176765442,"lat":22.285726094375427},"footprint":[[114.14291203022003,22.28575091297715],[114.14291203022003,22.285780695280607],[114.14305686950684,22.285775731563803],[114.14305686950684,22.285671493470247],[114.142906665802,22.28567645719076],[114.14291203022003,22.28575091297715]],"layoutDeclared":false,"initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-13","name":"拾光樓（合成）","address":"演示街區 13 號 · 虛構地址","coordinates":{"lng":114.13944393396378,"lat":22.284753202106018},"footprint":[[114.13941442966461,22.284693637093838],[114.13939833641052,22.284693637093838],[114.13935005664825,22.284668818315083],[114.13934469223022,22.284678745827122],[114.13930177688599,22.28465392704571],[114.13926959037781,22.2847184558682],[114.13938224315643,22.284768093403684],[114.13938760757446,22.284852477173544],[114.13942515850067,22.284847513423784],[114.13942515850067,22.284857440923133],[114.13946807384491,22.284857440923133],[114.13946270942688,22.284847513423784],[114.13950026035309,22.284842549673854],[114.13949489593506,22.284768093403684],[114.13961827754974,22.284698600849055],[114.13958609104156,22.2846489632889],[114.13954317569733,22.284668818315083],[114.1395378112793,22.284658890802348],[114.13947880268097,22.284688673338437],[114.13946270942688,22.284693637093838],[114.13946270942688,22.284673782071195],[114.13940906524658,22.284673782071195],[114.13941442966461,22.284693637093838]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":13},{"isSynthetic":true,"provisional":true,"id":"district-14","name":"和煦樓（合成）","address":"演示街區 14 號 · 虛構地址","coordinates":{"lng":114.14081990718842,"lat":22.284790430151403},"footprint":[[114.14072871208191,22.284604289469698],[114.14073944091797,22.28498649835042],[114.14082527160645,22.284981534605436],[114.14082527160645,22.28496664336936],[114.14091110229492,22.28496664336936],[114.14090037345886,22.284594361952387],[114.14087355136871,22.284594361952387],[114.14087355136871,22.284604289469698],[114.14072871208191,22.284604289469698]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":6},{"isSynthetic":true,"provisional":true,"id":"district-15","name":"榕溪樓（合成）","address":"演示街區 15 號 · 虛構地址","coordinates":{"lng":114.1420429944992,"lat":22.284894669027736},"footprint":[[114.14195716381073,22.284951752131732],[114.14212882518768,22.284946788385483],[114.14212346076965,22.28483758592374],[114.142005443573,22.28483758592374],[114.142005443573,22.284877295919713],[114.14195716381073,22.284882259668407],[114.14195716381073,22.284951752131732]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":8},{"isSynthetic":true,"provisional":true,"id":"district-16","name":"微光樓（合成）","address":"演示街區 16 號 · 虛構地址","coordinates":{"lng":114.14333045482635,"lat":22.284941824574837},"footprint":[[114.14327681064606,22.285075845730304],[114.14339482784271,22.285070881988474],[114.14337873458862,22.28480780341937],[114.14326608181,22.284812767170536],[114.14327681064606,22.285075845730304]],"layoutDeclared":false,"initialCoverage":"UNKNOWN"}],"floors":[{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f1","buildingId":"bldg-yu-an","label":"1F","level":1},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f2","buildingId":"bldg-yu-an","label":"2F","level":2},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f3","buildingId":"bldg-yu-an","label":"3F","level":3},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f4","buildingId":"bldg-yu-an","label":"4F","level":4},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f5","buildingId":"bldg-yu-an","label":"5F","level":5},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f6","buildingId":"bldg-yu-an","label":"6F","level":6},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f7","buildingId":"bldg-yu-an","label":"7F","level":7},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f8","buildingId":"bldg-yu-an","label":"8F","level":8},{"isSynthetic":true,"provisional":true,"id":"bldg-hoi-king-f1","buildingId":"bldg-hoi-king","label":"1F","level":1},{"isSynthetic":true,"provisional":true,"id":"bldg-hoi-king-f2","buildingId":"bldg-hoi-king","label":"2F","level":2},{"isSynthetic":true,"provisional":true,"id":"district-01-f1","buildingId":"district-01","level":1,"label":"1 樓"},{"isSynthetic":true,"provisional":true,"id":"district-01-f2","buildingId":"district-01","level":2,"label":"2 樓"},{"isSynthetic":true,"provisional":true,"id":"district-01-f3","buildingId":"district-01","level":3,"label":"3 樓"},{"isSynthetic":true,"provisional":true,"id":"district-01-f4","buildingId":"district-01","level":4,"label":"4 樓"},{"isSynthetic":true,"provisional":true,"id":"district-01-f5","buildingId":"district-01","level":5,"label":"5 樓"},{"isSynthetic":true,"provisional":true,"id":"district-01-f6","buildingId":"district-01","level":6,"label":"6 樓"},{"isSynthetic":true,"provisional":true,"id":"district-01-f7","buildingId":"district-01","level":7,"label":"7 樓"},{"isSynthetic":true,"provisional":true,"id":"district-01-f8","buildingId":"district-01","level":8,"label":"8 樓"},{"isSynthetic":true,"provisional":true,"id":"district-01-f9","buildingId":"district-01","level":9,"label":"9 樓"},{"isSynthetic":true,"provisional":true,"id":"district-01-f10","buildingId":"district-01","level":10,"label":"10 樓"},{"isSynthetic":true,"provisional":true,"id":"district-02-f1","buildingId":"district-02","level":1,"label":"1 樓"},{"isSynthetic":true,"provisional":true,"id":"district-02-f2","buildingId":"district-02","level":2,"label":"2 樓"},{"isSynthetic":true,"provisional":true,"id":"district-02-f3","buildingId":"district-02","level":3,"label":"3 樓"},{"isSynthetic":true,"provisional":true,"id":"district-02-f4","buildingId":"district-02","level":4,"label":"4 樓"},{"isSynthetic":true,"provisional":true,"id":"district-02-f5","buildingId":"district-02","level":5,"label":"5 樓"},{"isSynthetic":true,"provisional":true,"id":"district-02-f6","buildingId":"district-02","level":6,"label":"6 樓"},{"isSynthetic":true,"provisional":true,"id":"district-02-f7","buildingId":"district-02","level":7,"label":"7 樓"},{"isSynthetic":true,"provisional":true,"id":"district-03-f1","buildingId":"district-03","level":1,"label":"1 樓"},{"isSynthetic":true,"provisional":true,"id":"district-03-f2","buildingId":"district-03","level":2,"label":"2 樓"},{"isSynthetic":true,"provisional":true,"id":"district-03-f3","buildingId":"district-03","level":3,"label":"3 樓"},{"isSynthetic":true,"provisional":true,"id":"district-03-f4","buildingId":"district-03","level":4,"label":"4 樓"},{"isSynthetic":true,"provisional":true,"id":"district-03-f5","buildingId":"district-03","level":5,"label":"5 樓"},{"isSynthetic":true,"provisional":true,"id":"district-03-f6","buildingId":"district-03","level":6,"label":"6 樓"},{"isSynthetic":true,"provisional":true,"id":"district-03-f7","buildingId":"district-03","level":7,"label":"7 樓"},{"isSynthetic":true,"provisional":true,"id":"district-03-f8","buildingId":"district-03","level":8,"label":"8 樓"},{"isSynthetic":true,"provisional":true,"id":"district-03-f9","buildingId":"district-03","level":9,"label":"9 樓"},{"isSynthetic":true,"provisional":true,"id":"district-03-f10","buildingId":"district-03","level":10,"label":"10 樓"},{"isSynthetic":true,"provisional":true,"id":"district-03-f11","buildingId":"district-03","level":11,"label":"11 樓"},{"isSynthetic":true,"provisional":true,"id":"district-03-f12","buildingId":"district-03","level":12,"label":"12 樓"},{"isSynthetic":true,"provisional":true,"id":"district-04-f1","buildingId":"district-04","level":1,"label":"1 樓"},{"isSynthetic":true,"provisional":true,"id":"district-04-f2","buildingId":"district-04","level":2,"label":"2 樓"},{"isSynthetic":true,"provisional":true,"id":"district-04-f3","buildingId":"district-04","level":3,"label":"3 樓"},{"isSynthetic":true,"provisional":true,"id":"district-04-f4","buildingId":"district-04","level":4,"label":"4 樓"},{"isSynthetic":true,"provisional":true,"id":"district-04-f5","buildingId":"district-04","level":5,"label":"5 樓"},{"isSynthetic":true,"provisional":true,"id":"district-05-f1","buildingId":"district-05","level":1,"label":"1 樓"},{"isSynthetic":true,"provisional":true,"id":"district-05-f2","buildingId":"district-05","level":2,"label":"2 樓"},{"isSynthetic":true,"provisional":true,"id":"district-05-f3","buildingId":"district-05","level":3,"label":"3 樓"},{"isSynthetic":true,"provisional":true,"id":"district-05-f4","buildingId":"district-05","level":4,"label":"4 樓"},{"isSynthetic":true,"provisional":true,"id":"district-05-f5","buildingId":"district-05","level":5,"label":"5 樓"},{"isSynthetic":true,"provisional":true,"id":"district-05-f6","buildingId":"district-05","level":6,"label":"6 樓"},{"isSynthetic":true,"provisional":true,"id":"district-05-f7","buildingId":"district-05","level":7,"label":"7 樓"},{"isSynthetic":true,"provisional":true,"id":"district-05-f8","buildingId":"district-05","level":8,"label":"8 樓"},{"isSynthetic":true,"provisional":true,"id":"district-05-f9","buildingId":"district-05","level":9,"label":"9 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f1","buildingId":"district-07","level":1,"label":"1 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f2","buildingId":"district-07","level":2,"label":"2 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f3","buildingId":"district-07","level":3,"label":"3 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f4","buildingId":"district-07","level":4,"label":"4 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f5","buildingId":"district-07","level":5,"label":"5 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f6","buildingId":"district-07","level":6,"label":"6 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f7","buildingId":"district-07","level":7,"label":"7 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f8","buildingId":"district-07","level":8,"label":"8 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f9","buildingId":"district-07","level":9,"label":"9 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f10","buildingId":"district-07","level":10,"label":"10 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f11","buildingId":"district-07","level":11,"label":"11 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f12","buildingId":"district-07","level":12,"label":"12 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f13","buildingId":"district-07","level":13,"label":"13 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f14","buildingId":"district-07","level":14,"label":"14 樓"},{"isSynthetic":true,"provisional":true,"id":"district-08-f1","buildingId":"district-08","level":1,"label":"1 樓"},{"isSynthetic":true,"provisional":true,"id":"district-08-f2","buildingId":"district-08","level":2,"label":"2 樓"},{"isSynthetic":true,"provisional":true,"id":"district-08-f3","buildingId":"district-08","level":3,"label":"3 樓"},{"isSynthetic":true,"provisional":true,"id":"district-08-f4","buildingId":"district-08","level":4,"label":"4 樓"},{"isSynthetic":true,"provisional":true,"id":"district-08-f5","buildingId":"district-08","level":5,"label":"5 樓"},{"isSynthetic":true,"provisional":true,"id":"district-08-f6","buildingId":"district-08","level":6,"label":"6 樓"},{"isSynthetic":true,"provisional":true,"id":"district-09-f1","buildingId":"district-09","level":1,"label":"1 樓"},{"isSynthetic":true,"provisional":true,"id":"district-09-f2","buildingId":"district-09","level":2,"label":"2 樓"},{"isSynthetic":true,"provisional":true,"id":"district-09-f3","buildingId":"district-09","level":3,"label":"3 樓"},{"isSynthetic":true,"provisional":true,"id":"district-09-f4","buildingId":"district-09","level":4,"label":"4 樓"},{"isSynthetic":true,"provisional":true,"id":"district-09-f5","buildingId":"district-09","level":5,"label":"5 樓"},{"isSynthetic":true,"provisional":true,"id":"district-09-f6","buildingId":"district-09","level":6,"label":"6 樓"},{"isSynthetic":true,"provisional":true,"id":"district-09-f7","buildingId":"district-09","level":7,"label":"7 樓"},{"isSynthetic":true,"provisional":true,"id":"district-09-f8","buildingId":"district-09","level":8,"label":"8 樓"},{"isSynthetic":true,"provisional":true,"id":"district-10-f1","buildingId":"district-10","level":1,"label":"1 樓"},{"isSynthetic":true,"provisional":true,"id":"district-10-f2","buildingId":"district-10","level":2,"label":"2 樓"},{"isSynthetic":true,"provisional":true,"id":"district-10-f3","buildingId":"district-10","level":3,"label":"3 樓"},{"isSynthetic":true,"provisional":true,"id":"district-10-f4","buildingId":"district-10","level":4,"label":"4 樓"},{"isSynthetic":true,"provisional":true,"id":"district-11-f1","buildingId":"district-11","level":1,"label":"1 樓"},{"isSynthetic":true,"provisional":true,"id":"district-11-f2","buildingId":"district-11","level":2,"label":"2 樓"},{"isSynthetic":true,"provisional":true,"id":"district-11-f3","buildingId":"district-11","level":3,"label":"3 樓"},{"isSynthetic":true,"provisional":true,"id":"district-11-f4","buildingId":"district-11","level":4,"label":"4 樓"},{"isSynthetic":true,"provisional":true,"id":"district-11-f5","buildingId":"district-11","level":5,"label":"5 樓"},{"isSynthetic":true,"provisional":true,"id":"district-11-f6","buildingId":"district-11","level":6,"label":"6 樓"},{"isSynthetic":true,"provisional":true,"id":"district-11-f7","buildingId":"district-11","level":7,"label":"7 樓"},{"isSynthetic":true,"provisional":true,"id":"district-11-f8","buildingId":"district-11","level":8,"label":"8 樓"},{"isSynthetic":true,"provisional":true,"id":"district-11-f9","buildingId":"district-11","level":9,"label":"9 樓"},{"isSynthetic":true,"provisional":true,"id":"district-11-f10","buildingId":"district-11","level":10,"label":"10 樓"},{"isSynthetic":true,"provisional":true,"id":"district-11-f11","buildingId":"district-11","level":11,"label":"11 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f1","buildingId":"district-13","level":1,"label":"1 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f2","buildingId":"district-13","level":2,"label":"2 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f3","buildingId":"district-13","level":3,"label":"3 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f4","buildingId":"district-13","level":4,"label":"4 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f5","buildingId":"district-13","level":5,"label":"5 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f6","buildingId":"district-13","level":6,"label":"6 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f7","buildingId":"district-13","level":7,"label":"7 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f8","buildingId":"district-13","level":8,"label":"8 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f9","buildingId":"district-13","level":9,"label":"9 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f10","buildingId":"district-13","level":10,"label":"10 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f11","buildingId":"district-13","level":11,"label":"11 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f12","buildingId":"district-13","level":12,"label":"12 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f13","buildingI</x:v>
+        <x:v>{"schemaVersion":"0.1-demo","isSynthetic":true,"notice":"全區合成演示：20 個大廈位置用作介面測試；樓名、地址、樓層、單位、住戶及記錄均屬虛構，不代表地圖底圖中的真實建築或居民。依原紙本＋Excel 工作流設計，欄位仍待機構確認。","buildings":[{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an","name":"裕安樓","address":"西營盤示範街 1 號（合成）","layoutDeclared":true,"floorCount":8,"initialCoverage":"UNVISITED","coordinates":{"lng":114.14178818464279,"lat":22.286363930711317},"footprint":[[114.14168894290924,22.286500432351488],[114.1418981552124,22.286495468660235],[114.14189279079437,22.286227429071147],[114.14167821407318,22.286237356472498],[114.14168894290924,22.286500432351488]]},{"isSynthetic":true,"provisional":true,"id":"bldg-hoi-king","name":"海景樓","address":"西營盤示範街 8 號（合成）","layoutDeclared":true,"floorCount":2,"initialCoverage":"UNVISITED","coordinates":{"lng":114.14255797863007,"lat":22.28661211534631},"footprint":[[114.14262235164642,22.286664234063778],[114.14262235164642,22.286619560888553],[114.14259016513824,22.286624524575387],[114.14258480072021,22.286589778763798],[114.14263308048248,22.286589778763798],[114.14263308048248,22.286555032943582],[114.14248287677765,22.286559996632704],[114.14248287677765,22.28659474245171],[114.14253115653992,22.28659474245171],[114.14253115653992,22.286624524575387],[114.14249897003174,22.286624524575387],[114.14249897003174,22.286669197749035],[114.14262235164642,22.286664234063778]]},{"isSynthetic":true,"provisional":true,"id":"bldg-duk-cheong","name":"德昌樓","address":"西營盤示範街 16 號（合成）","layoutDeclared":false,"initialCoverage":"UNKNOWN","coordinates":{"lng":114.14136976003647,"lat":22.286808180844794},"footprint":[[114.1414475440979,22.286733725641312],[114.14129197597504,22.286733725641312],[114.14129197597504,22.286882636048276],[114.1414475440979,22.286877672370593],[114.1414475440979,22.286733725641312]]},{"isSynthetic":true,"provisional":true,"id":"bldg-on-wo","name":"安和樓","address":"西營盤示範街 24 號（合成）","layoutDeclared":false,"initialCoverage":"UNKNOWN","coordinates":{"lng":114.14208590984344,"lat":22.28576580411479},"footprint":[[114.14213418960571,22.285825368723906],[114.14212882518768,22.28570127579063],[114.14203763008118,22.285706239510063],[114.1420429944992,22.285830332438948],[114.14213418960571,22.285825368723906]]},{"isSynthetic":true,"provisional":true,"id":"district-01","name":"晴里樓","address":"演示街區 01 號 · 虛構地址","coordinates":{"lng":114.13954049348831,"lat":22.287835658837054},"footprint":[[114.13945734500885,22.287890258967195],[114.13946807384491,22.287865440755937],[114.13947880268097,22.28787040439856],[114.13946270942688,22.287920040814882],[114.1395378112793,22.287939895376482],[114.13955390453339,22.287890258967195],[114.13956463336945,22.287890258967195],[114.13954854011536,22.287944859016434],[114.13962364196777,22.28796471357451],[114.13963973522186,22.287910113533016],[114.13965582847595,22.28791507717405],[114.13966655731201,22.28787536804097],[114.13965046405792,22.28787040439856],[114.13966119289398,22.287835658896626],[114.1396826505661,22.287840622540287],[114.13970410823822,22.28778105880474],[114.13943588733673,22.287706604099597],[114.1393768787384,22.28789522260891],[114.13945198059082,22.28791507717405],[114.13945734500885,22.287890258967195]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":10},{"isSynthetic":true,"provisional":true,"id":"district-02","name":"青禾樓","address":"演示街區 02 號 · 虛構地址","coordinates":{"lng":114.14060264825821,"lat":22.287644558357755},"footprint":[[114.14048731327057,22.28780091338608],[114.14061069488525,22.28783069525278],[114.14062678813934,22.28778105880474],[114.1406911611557,22.287795949740996],[114.14071798324585,22.287696676802582],[114.14065897464752,22.28768178585574],[114.14071261882782,22.28749316705843],[114.1405838727951,22.28745842146273],[114.14048731327057,22.28780091338608]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":7},{"isSynthetic":true,"provisional":true,"id":"district-03","name":"映榕樓","address":"演示街區 03 號 · 虛構地址","coordinates":{"lng":114.14200276136398,"lat":22.287753758732258},"footprint":[[114.14189279079437,22.287686749504857],[114.1418981552124,22.287825731608777],[114.1421127319336,22.28782076796459],[114.14210736751556,22.28768178585574],[114.14189279079437,22.287686749504857]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":12},{"isSynthetic":true,"provisional":true,"id":"district-04","name":"小滿樓","address":"演示街區 04 號 · 虛構地址","coordinates":{"lng":114.14324462413788,"lat":22.287714049553372},"footprint":[[114.14331436157227,22.28778105880474],[114.14330899715424,22.28764207665641],[114.14319097995758,22.287647040306936],[114.14319097995758,22.287751276927438],[114.14317488670349,22.287751276927438],[114.14317488670349,22.287786022450334],[114.14331436157227,22.28778105880474]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":5},{"isSynthetic":true,"provisional":true,"id":"district-05","name":"常悅樓","address":"演示街區 05 號 · 虛構地址","coordinates":{"lng":114.13936883211136,"lat":22.286842926596464},"footprint":[[114.13924276828766,22.28687270869274],[114.13945734500885,22.286927309139443],[114.13949489593506,22.286818108224736],[114.13928031921387,22.286758544053484],[114.13924276828766,22.28687270869274]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":9},{"isSynthetic":true,"provisional":true,"id":"district-06","name":"知秋樓","address":"演示街區 06 號 · 虛構地址","coordinates":{"lng":114.14092719554901,"lat":22.286840444772693},"footprint":[[114.14082527160645,22.28683796294284],[114.14087355136871,22.28683796294284],[114.14087355136871,22.2868925634031],[114.14098620414734,22.286887599725773],[114.14098620414734,22.28683299926358],[114.14102911949158,22.28683299926358],[114.14102911949158,22.286788326142286],[114.14082527160645,22.286793289823123],[114.14082527160645,22.28683796294284]],"layoutDeclared":false,"initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-07","name":"晴川樓","address":"演示街區 07 號 · 虛構地址","coordinates":{"lng":114.14216101169586,"lat":22.286723798239954},"footprint":[[114.14209127426147,22.286624524575387],[114.14209127426147,22.28665430669274],[114.14210200309753,22.28665430669274],[114.14210736751556,22.286793289823123],[114.1420966386795,22.286793289823123],[114.1420966386795,22.28682307190452],[114.14218246936798,22.28682307190452],[114.14217174053192,22.286763507735387],[114.14223074913025,22.286763507735387],[114.14223074913025,22.286674161434107],[114.14217174053192,22.286674161434107],[114.14217710494995,22.286624524575387],[114.14209127426147,22.286624524575387]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":14},{"isSynthetic":true,"provisional":true,"id":"district-08","name":"穗安樓","address":"演示街區 08 號 · 虛構地址","coordinates":{"lng":114.14348870515823,"lat":22.286728761932885},"footprint":[[114.14357721805573,22.286644379321004],[114.14339482784271,22.286649343006957],[114.14340019226074,22.286813144544766],[114.14358258247375,22.286808180864625],[114.14357721805573,22.286644379321004]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":6},{"isSynthetic":true,"provisional":true,"id":"district-09","name":"棠和樓","address":"演示街區 09 號 · 虛構地址","coordinates":{"lng":114.13955926895142,"lat":22.28589237884831},"footprint":[[114.13951098918915,22.28595442525767],[114.13961291313171,22.28594449783624],[114.13961291313171,22.28592960670275],[114.13965046405792,22.285924642991233],[114.13964509963989,22.285879969579653],[114.13960754871368,22.28588493329275],[114.13960218429565,22.285830332438948],[114.13955926895142,22.28583529615382],[114.13956463336945,22.285870042152922],[114.13954317569733,22.285870042152922],[114.13954317569733,22.28583529615382],[114.13950026035309,22.285840259868493],[114.13950562477112,22.285894860718443],[114.13946807384491,22.285894860718443],[114.13947343826294,22.285939534125234],[114.13951098918915,22.285939534125234],[114.13951098918915,22.28595442525767]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":8},{"isSynthetic":true,"provisional":true,"id":"district-10","name":"日和樓","address":"演示街區 10 號 · 虛構地址","coordinates":{"lng":114.14058923721313,"lat":22.285837777977676},"footprint":[[114.1406375169754,22.285899824431013],[114.14064824581146,22.285899824431013],[114.14064288139343,22.28576580412968],[114.1406375169754,22.28576580412968],[114.14063215255737,22.285740985541267],[114.14057850837708,22.285745949259294],[114.14057850837708,22.285775731563803],[114.14056777954102,22.285775731563803],[114.14056241512299,22.285800550146064],[114.14053022861481,22.285800550146064],[114.14053022861481,22.285855151011503],[114.1405463218689,22.285855151011503],[114.1405463218689,22.285875005866373],[114.14053022861481,22.285875005866373],[114.14053559303284,22.285924642991233],[114.14062142372131,22.285934570414085],[114.14062142372131,22.28592960670275],[114.1406375169754,22.28592960670275],[114.1406375169754,22.285899824431013]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":4},{"isSynthetic":true,"provisional":true,"id":"district-11","name":"朗月樓","address":"演示街區 11 號 · 虛構地址","coordinates":{"lng":114.14172112941742,"lat":22.285909751848486},"footprint":[[114.14187133312225,22.2858650784393],[114.14156556129456,22.285875005866373],[114.14156556129456,22.28595442525767],[114.14187669754028,22.28594449783624],[114.14187133312225,22.2858650784393]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":11},{"isSynthetic":true,"provisional":true,"id":"district-12","name":"杏林樓","address":"演示街區 12 號 · 虛構地址","coordinates":{"lng":114.14298176765442,"lat":22.285726094375427},"footprint":[[114.14291203022003,22.28575091297715],[114.14291203022003,22.285780695280607],[114.14305686950684,22.285775731563803],[114.14305686950684,22.285671493470247],[114.142906665802,22.28567645719076],[114.14291203022003,22.28575091297715]],"layoutDeclared":false,"initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-13","name":"拾光樓","address":"演示街區 13 號 · 虛構地址","coordinates":{"lng":114.13944393396378,"lat":22.284753202106018},"footprint":[[114.13941442966461,22.284693637093838],[114.13939833641052,22.284693637093838],[114.13935005664825,22.284668818315083],[114.13934469223022,22.284678745827122],[114.13930177688599,22.28465392704571],[114.13926959037781,22.2847184558682],[114.13938224315643,22.284768093403684],[114.13938760757446,22.284852477173544],[114.13942515850067,22.284847513423784],[114.13942515850067,22.284857440923133],[114.13946807384491,22.284857440923133],[114.13946270942688,22.284847513423784],[114.13950026035309,22.284842549673854],[114.13949489593506,22.284768093403684],[114.13961827754974,22.284698600849055],[114.13958609104156,22.2846489632889],[114.13954317569733,22.284668818315083],[114.1395378112793,22.284658890802348],[114.13947880268097,22.284688673338437],[114.13946270942688,22.284693637093838],[114.13946270942688,22.284673782071195],[114.13940906524658,22.284673782071195],[114.13941442966461,22.284693637093838]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":13},{"isSynthetic":true,"provisional":true,"id":"district-14","name":"和煦樓","address":"演示街區 14 號 · 虛構地址","coordinates":{"lng":114.14081990718842,"lat":22.284790430151403},"footprint":[[114.14072871208191,22.284604289469698],[114.14073944091797,22.28498649835042],[114.14082527160645,22.284981534605436],[114.14082527160645,22.28496664336936],[114.14091110229492,22.28496664336936],[114.14090037345886,22.284594361952387],[114.14087355136871,22.284594361952387],[114.14087355136871,22.284604289469698],[114.14072871208191,22.284604289469698]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":6},{"isSynthetic":true,"provisional":true,"id":"district-15","name":"榕溪樓","address":"演示街區 15 號 · 虛構地址","coordinates":{"lng":114.1420429944992,"lat":22.284894669027736},"footprint":[[114.14195716381073,22.284951752131732],[114.14212882518768,22.284946788385483],[114.14212346076965,22.28483758592374],[114.142005443573,22.28483758592374],[114.142005443573,22.284877295919713],[114.14195716381073,22.284882259668407],[114.14195716381073,22.284951752131732]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":8},{"isSynthetic":true,"provisional":true,"id":"district-16","name":"微光樓","address":"演示街區 16 號 · 虛構地址","coordinates":{"lng":114.14333045482635,"lat":22.284941824574837},"footprint":[[114.14327681064606,22.285075845730304],[114.14339482784271,22.285070881988474],[114.14337873458862,22.28480780341937],[114.14326608181,22.284812767170536],[114.14327681064606,22.285075845730304]],"layoutDeclared":false,"initialCoverage":"UNKNOWN"}],"floors":[{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f1","buildingId":"bldg-yu-an","label":"1F","level":1},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f2","buildingId":"bldg-yu-an","label":"2F","level":2},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f3","buildingId":"bldg-yu-an","label":"3F","level":3},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f4","buildingId":"bldg-yu-an","label":"4F","level":4},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f5","buildingId":"bldg-yu-an","label":"5F","level":5},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f6","buildingId":"bldg-yu-an","label":"6F","level":6},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f7","buildingId":"bldg-yu-an","label":"7F","level":7},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f8","buildingId":"bldg-yu-an","label":"8F","level":8},{"isSynthetic":true,"provisional":true,"id":"bldg-hoi-king-f1","buildingId":"bldg-hoi-king","label":"1F","level":1},{"isSynthetic":true,"provisional":true,"id":"bldg-hoi-king-f2","buildingId":"bldg-hoi-king","label":"2F","level":2},{"isSynthetic":true,"provisional":true,"id":"district-01-f1","buildingId":"district-01","level":1,"label":"1 樓"},{"isSynthetic":true,"provisional":true,"id":"district-01-f2","buildingId":"district-01","level":2,"label":"2 樓"},{"isSynthetic":true,"provisional":true,"id":"district-01-f3","buildingId":"district-01","level":3,"label":"3 樓"},{"isSynthetic":true,"provisional":true,"id":"district-01-f4","buildingId":"district-01","level":4,"label":"4 樓"},{"isSynthetic":true,"provisional":true,"id":"district-01-f5","buildingId":"district-01","level":5,"label":"5 樓"},{"isSynthetic":true,"provisional":true,"id":"district-01-f6","buildingId":"district-01","level":6,"label":"6 樓"},{"isSynthetic":true,"provisional":true,"id":"district-01-f7","buildingId":"district-01","level":7,"label":"7 樓"},{"isSynthetic":true,"provisional":true,"id":"district-01-f8","buildingId":"district-01","level":8,"label":"8 樓"},{"isSynthetic":true,"provisional":true,"id":"district-01-f9","buildingId":"district-01","level":9,"label":"9 樓"},{"isSynthetic":true,"provisional":true,"id":"district-01-f10","buildingId":"district-01","level":10,"label":"10 樓"},{"isSynthetic":true,"provisional":true,"id":"district-02-f1","buildingId":"district-02","level":1,"label":"1 樓"},{"isSynthetic":true,"provisional":true,"id":"district-02-f2","buildingId":"district-02","level":2,"label":"2 樓"},{"isSynthetic":true,"provisional":true,"id":"district-02-f3","buildingId":"district-02","level":3,"label":"3 樓"},{"isSynthetic":true,"provisional":true,"id":"district-02-f4","buildingId":"district-02","level":4,"label":"4 樓"},{"isSynthetic":true,"provisional":true,"id":"district-02-f5","buildingId":"district-02","level":5,"label":"5 樓"},{"isSynthetic":true,"provisional":true,"id":"district-02-f6","buildingId":"district-02","level":6,"label":"6 樓"},{"isSynthetic":true,"provisional":true,"id":"district-02-f7","buildingId":"district-02","level":7,"label":"7 樓"},{"isSynthetic":true,"provisional":true,"id":"district-03-f1","buildingId":"district-03","level":1,"label":"1 樓"},{"isSynthetic":true,"provisional":true,"id":"district-03-f2","buildingId":"district-03","level":2,"label":"2 樓"},{"isSynthetic":true,"provisional":true,"id":"district-03-f3","buildingId":"district-03","level":3,"label":"3 樓"},{"isSynthetic":true,"provisional":true,"id":"district-03-f4","buildingId":"district-03","level":4,"label":"4 樓"},{"isSynthetic":true,"provisional":true,"id":"district-03-f5","buildingId":"district-03","level":5,"label":"5 樓"},{"isSynthetic":true,"provisional":true,"id":"district-03-f6","buildingId":"district-03","level":6,"label":"6 樓"},{"isSynthetic":true,"provisional":true,"id":"district-03-f7","buildingId":"district-03","level":7,"label":"7 樓"},{"isSynthetic":true,"provisional":true,"id":"district-03-f8","buildingId":"district-03","level":8,"label":"8 樓"},{"isSynthetic":true,"provisional":true,"id":"district-03-f9","buildingId":"district-03","level":9,"label":"9 樓"},{"isSynthetic":true,"provisional":true,"id":"district-03-f10","buildingId":"district-03","level":10,"label":"10 樓"},{"isSynthetic":true,"provisional":true,"id":"district-03-f11","buildingId":"district-03","level":11,"label":"11 樓"},{"isSynthetic":true,"provisional":true,"id":"district-03-f12","buildingId":"district-03","level":12,"label":"12 樓"},{"isSynthetic":true,"provisional":true,"id":"district-04-f1","buildingId":"district-04","level":1,"label":"1 樓"},{"isSynthetic":true,"provisional":true,"id":"district-04-f2","buildingId":"district-04","level":2,"label":"2 樓"},{"isSynthetic":true,"provisional":true,"id":"district-04-f3","buildingId":"district-04","level":3,"label":"3 樓"},{"isSynthetic":true,"provisional":true,"id":"district-04-f4","buildingId":"district-04","level":4,"label":"4 樓"},{"isSynthetic":true,"provisional":true,"id":"district-04-f5","buildingId":"district-04","level":5,"label":"5 樓"},{"isSynthetic":true,"provisional":true,"id":"district-05-f1","buildingId":"district-05","level":1,"label":"1 樓"},{"isSynthetic":true,"provisional":true,"id":"district-05-f2","buildingId":"district-05","level":2,"label":"2 樓"},{"isSynthetic":true,"provisional":true,"id":"district-05-f3","buildingId":"district-05","level":3,"label":"3 樓"},{"isSynthetic":true,"provisional":true,"id":"district-05-f4","buildingId":"district-05","level":4,"label":"4 樓"},{"isSynthetic":true,"provisional":true,"id":"district-05-f5","buildingId":"district-05","level":5,"label":"5 樓"},{"isSynthetic":true,"provisional":true,"id":"district-05-f6","buildingId":"district-05","level":6,"label":"6 樓"},{"isSynthetic":true,"provisional":true,"id":"district-05-f7","buildingId":"district-05","level":7,"label":"7 樓"},{"isSynthetic":true,"provisional":true,"id":"district-05-f8","buildingId":"district-05","level":8,"label":"8 樓"},{"isSynthetic":true,"provisional":true,"id":"district-05-f9","buildingId":"district-05","level":9,"label":"9 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f1","buildingId":"district-07","level":1,"label":"1 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f2","buildingId":"district-07","level":2,"label":"2 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f3","buildingId":"district-07","level":3,"label":"3 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f4","buildingId":"district-07","level":4,"label":"4 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f5","buildingId":"district-07","level":5,"label":"5 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f6","buildingId":"district-07","level":6,"label":"6 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f7","buildingId":"district-07","level":7,"label":"7 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f8","buildingId":"district-07","level":8,"label":"8 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f9","buildingId":"district-07","level":9,"label":"9 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f10","buildingId":"district-07","level":10,"label":"10 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f11","buildingId":"district-07","level":11,"label":"11 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f12","buildingId":"district-07","level":12,"label":"12 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f13","buildingId":"district-07","level":13,"label":"13 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f14","buildingId":"district-07","level":14,"label":"14 樓"},{"isSynthetic":true,"provisional":true,"id":"district-08-f1","buildingId":"district-08","level":1,"label":"1 樓"},{"isSynthetic":true,"provisional":true,"id":"district-08-f2","buildingId":"district-08","level":2,"label":"2 樓"},{"isSynthetic":true,"provisional":true,"id":"district-08-f3","buildingId":"district-08","level":3,"label":"3 樓"},{"isSynthetic":true,"provisional":true,"id":"district-08-f4","buildingId":"district-08","level":4,"label":"4 樓"},{"isSynthetic":true,"provisional":true,"id":"district-08-f5","buildingId":"district-08","level":5,"label":"5 樓"},{"isSynthetic":true,"provisional":true,"id":"district-08-f6","buildingId":"district-08","level":6,"label":"6 樓"},{"isSynthetic":true,"provisional":true,"id":"district-09-f1","buildingId":"district-09","level":1,"label":"1 樓"},{"isSynthetic":true,"provisional":true,"id":"district-09-f2","buildingId":"district-09","level":2,"label":"2 樓"},{"isSynthetic":true,"provisional":true,"id":"district-09-f3","buildingId":"district-09","level":3,"label":"3 樓"},{"isSynthetic":true,"provisional":true,"id":"district-09-f4","buildingId":"district-09","level":4,"label":"4 樓"},{"isSynthetic":true,"provisional":true,"id":"district-09-f5","buildingId":"district-09","level":5,"label":"5 樓"},{"isSynthetic":true,"provisional":true,"id":"district-09-f6","buildingId":"district-09","level":6,"label":"6 樓"},{"isSynthetic":true,"provisional":true,"id":"district-09-f7","buildingId":"district-09","level":7,"label":"7 樓"},{"isSynthetic":true,"provisional":true,"id":"district-09-f8","buildingId":"district-09","level":8,"label":"8 樓"},{"isSynthetic":true,"provisional":true,"id":"district-10-f1","buildingId":"district-10","level":1,"label":"1 樓"},{"isSynthetic":true,"provisional":true,"id":"district-10-f2","buildingId":"district-10","level":2,"label":"2 樓"},{"isSynthetic":true,"provisional":true,"id":"district-10-f3","buildingId":"district-10","level":3,"label":"3 樓"},{"isSynthetic":true,"provisional":true,"id":"district-10-f4","buildingId":"district-10","level":4,"label":"4 樓"},{"isSynthetic":true,"provisional":true,"id":"district-11-f1","buildingId":"district-11","level":1,"label":"1 樓"},{"isSynthetic":true,"provisional":true,"id":"district-11-f2","buildingId":"district-11","level":2,"label":"2 樓"},{"isSynthetic":true,"provisional":true,"id":"district-11-f3","buildingId":"district-11","level":3,"label":"3 樓"},{"isSynthetic":true,"provisional":true,"id":"district-11-f4","buildingId":"district-11","level":4,"label":"4 樓"},{"isSynthetic":true,"provisional":true,"id":"district-11-f5","buildingId":"district-11","level":5,"label":"5 樓"},{"isSynthetic":true,"provisional":true,"id":"district-11-f6","buildingId":"district-11","level":6,"label":"6 樓"},{"isSynthetic":true,"provisional":true,"id":"district-11-f7","buildingId":"district-11","level":7,"label":"7 樓"},{"isSynthetic":true,"provisional":true,"id":"district-11-f8","buildingId":"district-11","level":8,"label":"8 樓"},{"isSynthetic":true,"provisional":true,"id":"district-11-f9","buildingId":"district-11","level":9,"label":"9 樓"},{"isSynthetic":true,"provisional":true,"id":"district-11-f10","buildingId":"district-11","level":10,"label":"10 樓"},{"isSynthetic":true,"provisional":true,"id":"district-11-f11","buildingId":"district-11","level":11,"label":"11 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f1","buildingId":"district-13","level":1,"label":"1 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f2","buildingId":"district-13","level":2,"label":"2 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f3","buildingId":"district-13","level":3,"label":"3 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f4","buildingId":"district-13","level":4,"label":"4 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f5","buildingId":"district-13","level":5,"label":"5 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f6","buildingId":"district-13","level":6,"label":"6 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f7","buildingId":"district-13","level":7,"label":"7 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f8","buildingId":"district-13","level":8,"label":"8 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f9","buildingId":"district-13","level":9,"label":"9 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f10","buildingId":"district-13","level":10,"label":"10 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f11","buildingId":"district-13","level":11,"label":"11 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f12","buildingId":"district-13","level":12,"label":"12 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f13","buildingI</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="25" customHeight="1">
@@ -19245,7 +19245,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B10" s="37" t="str">
-        <x:v>rage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-13-f4-B","buildingId":"district-13","floorId":"district-13-f4","label":"4樓 B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-13-f5-A","buildingId":"district-13","floorId":"district-13-f5","label":"5樓 A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-13-f5-B","buildingId":"district-13","floorId":"district-13-f5","label":"5樓 B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-13-f6-A","buildingId":"district-13","floorId":"district-13-f6","label":"6樓 A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-13-f6-B","buildingId":"district-13","floorId":"district-13-f6","label":"6樓 B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-13-f7-A","buildingId":"district-13","floorId":"district-13-f7","label":"7樓 A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-13-f7-B","buildingId":"district-13","floorId":"district-13-f7","label":"7樓 B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-13-f8-A","buildingId":"district-13","floorId":"district-13-f8","label":"8樓 A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-13-f8-B","buildingId":"district-13","floorId":"district-13-f8","label":"8樓 B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-13-f9-A","buildingId":"district-13","floorId":"district-13-f9","label":"9樓 A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-13-f9-B","buildingId":"district-13","floorId":"district-13-f9","label":"9樓 B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-13-f10-A","buildingId":"district-13","floorId":"district-13-f10","label":"10樓 A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-13-f10-B","buildingId":"district-13","floorId":"district-13-f10","label":"10樓 B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-13-f11-A","buildingId":"district-13","floorId":"district-13-f11","label":"11樓 A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-13-f11-B","buildingId":"district-13","floorId":"district-13-f11","label":"11樓 B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-13-f12-A","buildingId":"district-13","floorId":"district-13-f12","label":"12樓 A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-13-f12-B","buildingId":"district-13","floorId":"district-13-f12","label":"12樓 B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-13-f13-A","buildingId":"district-13","floorId":"district-13-f13","label":"13樓 A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-13-f13-B","buildingId":"district-13","floorId":"district-13-f13","label":"13樓 B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-14-f1-A","buildingId":"district-14","floorId":"district-14-f1","label":"1樓 A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-14-f1-B","buildingId":"district-14","floorId":"district-14-f1","label":"1樓 B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-14-f1-C","buildingId":"district-14","floorId":"district-14-f1","label":"1樓 C室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-14-f1-D","buildingId":"district-14","floorId":"district-14-f1","label":"1樓 D室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-14-f2-A","buildingId":"district-14","floorId":"district-14-f2","label":"2樓 A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-14-f2-B","buildingId":"district-14","floorId":"district-14-f2","label":"2樓 B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-14-f2-C","buildingId":"district-14","floorId":"district-14-f2","label":"2樓 C室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-14-f2-D","buildingId":"district-14","floorId":"district-14-f2","label":"2樓 D室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-14-f3-A","buildingId":"district-14","floorId":"district-14-f3","label":"3樓 A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-14-f3-B","buildingId":"district-14","floorId":"district-14-f3","label":"3樓 B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-14-f3-C","buildingId":"district-14","floorId":"district-14-f3","label":"3樓 C室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-14-f3-D","buildingId":"district-14","floorId":"district-14-f3","label":"3樓 D室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-14-f4-A","buildingId":"district-14","floorId":"district-14-f4","label":"4樓 A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-14-f4-B","buildingId":"district-14","floorId":"district-14-f4","label":"4樓 B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-14-f4-C","buildingId":"district-14","floorId":"district-14-f4","label":"4樓 C室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-14-f4-D","buildingId":"district-14","floorId":"district-14-f4","label":"4樓 D室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-14-f5-A","buildingId":"district-14","floorId":"district-14-f5","label":"5樓 A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-14-f5-B","buildingId":"district-14","floorId":"district-14-f5","label":"5樓 B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-14-f5-C","buildingId":"district-14","floorId":"district-14-f5","label":"5樓 C室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-14-f5-D","buildingId":"district-14","floorId":"district-14-f5","label":"5樓 D室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-14-f6-A","buildingId":"district-14","floorId":"district-14-f6","label":"6樓 A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-14-f6-B","buildingId":"district-14","floorId":"district-14-f6","label":"6樓 B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-14-f6-C","buildingId":"district-14","floorId":"district-14-f6","label":"6樓 C室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-14-f6-D","buildingId":"district-14","floorId":"district-14-f6","label":"6樓 D室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-15-f1-A","buildingId":"district-15","floorId":"district-15-f1","label":"1樓 A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-15-f1-B","buildingId":"district-15","floorId":"district-15-f1","label":"1樓 B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-15-f1-C","buildingId":"district-15","floorId":"district-15-f1","label":"1樓 C室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-15-f2-A","buildingId":"district-15","floorId":"district-15-f2","label":"2樓 A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-15-f2-B","buildingId":"district-15","floorId":"district-15-f2","label":"2樓 B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-15-f2-C","buildingId":"district-15","floorId":"district-15-f2","label":"2樓 C室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-15-f3-A","buildingId":"district-15","floorId":"district-15-f3","label":"3樓 A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-15-f3-B","buildingId":"district-15","floorId":"district-15-f3","label":"3樓 B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-15-f3-C","buildingId":"district-15","floorId":"district-15-f3","label":"3樓 C室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-15-f4-A","buildingId":"district-15","floorId":"district-15-f4","label":"4樓 A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-15-f4-B","buildingId":"district-15","floorId":"district-15-f4","label":"4樓 B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-15-f4-C","buildingId":"district-15","floorId":"district-15-f4","label":"4樓 C室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-15-f5-A","buildingId":"district-15","floorId":"district-15-f5","label":"5樓 A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-15-f5-B","buildingId":"district-15","floorId":"district-15-f5","label":"5樓 B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-15-f5-C","buildingId":"district-15","floorId":"district-15-f5","label":"5樓 C室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-15-f6-A","buildingId":"district-15","floorId":"district-15-f6","label":"6樓 A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-15-f6-B","buildingId":"district-15","floorId":"district-15-f6","label":"6樓 B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-15-f6-C","buildingId":"district-15","floorId":"district-15-f6","label":"6樓 C室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-15-f7-A","buildingId":"district-15","floorId":"district-15-f7","label":"7樓 A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-15-f7-B","buildingId":"district-15","floorId":"district-15-f7","label":"7樓 B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-15-f7-C","buildingId":"district-15","floorId":"district-15-f7","label":"7樓 C室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-15-f8-A","buildingId":"district-15","floorId":"district-15-f8","label":"8樓 A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-15-f8-B","buildingId":"district-15","floorId":"district-15-f8","label":"8樓 B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-15-f8-C","buildingId":"district-15","floorId":"district-15-f8","label":"8樓 C室","initialCoverage":"UNVISITED"}],"households":[{"isSynthetic":true,"provisional":true,"id":"household-lam","label":"林家庭（合成）"},{"isSynthetic":true,"provisional":true,"id":"district-01-hh1","label":"合成家庭 01-1"},{"isSynthetic":true,"provisional":true,"id":"district-01-hh2","label":"合成家庭 01-2"},{"isSynthetic":true,"provisional":true,"id":"district-01-hh3","label":"合成家庭 01-3"},{"isSynthetic":true,"provisional":true,"id":"district-02-hh1","label":"合成家庭 02-1"},{"isSynthetic":true,"provisional":true,"id":"district-02-hh2","label":"合成家庭 02-2"},{"isSynthetic":true,"provisional":true,"id":"district-02-hh3","label":"合成家庭 02-3"},{"isSynthetic":true,"provisional":true,"id":"district-03-hh1","label":"合成家庭 03-1"},{"isSynthetic":true,"provisional":true,"id":"district-03-hh2","label":"合成家庭 03-2"},{"isSynthetic":true,"provisional":true,"id":"district-03-hh3","label":"合成家庭 03-3"},{"isSynthetic":true,"provisional":true,"id":"district-04-hh1","label":"合成家庭 04-1"},{"isSynthetic":true,"provisional":true,"id":"district-04-hh2","label":"合成家庭 04-2"},{"isSynthetic":true,"provisional":true,"id":"district-04-hh3","label":"合成家庭 04-3"},{"isSynthetic":true,"provisional":true,"id":"district-05-hh1","label":"合成家庭 05-1"},{"isSynthetic":true,"provisional":true,"id":"district-05-hh2","label":"合成家庭 05-2"},{"isSynthetic":true,"provisional":true,"id":"district-05-hh3","label":"合成家庭 05-3"},{"isSynthetic":true,"provisional":true,"id":"district-06-hh1","label":"合成家庭 06-1"},{"isSynthetic":true,"provisional":true,"id":"district-06-hh2","label":"合成家庭 06-2"},{"isSynthetic":true,"provisional":true,"id":"district-07-hh1","label":"合成家庭 07-1"},{"isSynthetic":true,"provisional":true,"id":"district-07-hh2","label":"合成家庭 07-2"},{"isSynthetic":true,"provisional":true,"id":"district-07-hh3","label":"合成家庭 07-3"},{"isSynthetic":true,"provisional":true,"id":"district-08-hh1","label":"合成家庭 08-1"},{"isSynthetic":true,"provisional":true,"id":"district-08-hh2","label":"合成家庭 08-2"},{"isSynthetic":true,"provisional":true,"id":"district-08-hh3","label":"合成家庭 08-3"},{"isSynthetic":true,"provisional":true,"id":"district-09-hh1","label":"合成家庭 09-1"},{"isSynthetic":true,"provisional":true,"id":"district-09-hh2","label":"合成家庭 09-2"},{"isSynthetic":true,"provisional":true,"id":"district-09-hh3","label":"合成家庭 09-3"},{"isSynthetic":true,"provisional":true,"id":"district-10-hh1","label":"合成家庭 10-1"},{"isSynthetic":true,"provisional":true,"id":"district-10-hh2","label":"合成家庭 10-2"},{"isSynthetic":true,"provisional":true,"id":"district-10-hh3","label":"合成家庭 10-3"},{"isSynthetic":true,"provisional":true,"id":"district-11-hh1","label":"合成家庭 11-1"},{"isSynthetic":true,"provisional":true,"id":"district-11-hh2","label":"合成家庭 11-2"},{"isSynthetic":true,"provisional":true,"id":"district-11-hh3","label":"合成家庭 11-3"},{"isSynthetic":true,"provisional":true,"id":"district-12-hh1","label":"合成家庭 12-1"},{"isSynthetic":true,"provisional":true,"id":"district-12-hh2","label":"合成家庭 12-2"},{"isSynthetic":true,"provisional":true,"id":"district-13-hh1","label":"合成家庭 13-1"},{"isSynthetic":true,"provisional":true,"id":"district-13-hh2","label":"合成家庭 13-2"},{"isSynthetic":true,"provisional":true,"id":"district-13-hh3","label":"合成家庭 13-3"},{"isSynthetic":true,"provisional":true,"id":"district-15-hh1","label":"合成家庭 15-1"},{"isSynthetic":true,"provisional":true,"id":"district-15-hh2","label":"合成家庭 15-2"},{"isSynthetic":true,"provisional":true,"id":"district-15-hh3","label":"合成家庭 15-3"}],"people":[{"isSynthetic":true,"provisional":true,"id":"person-lam","displayName":"林女士（合成）"},{"isSynthetic":true,"provisional":true,"id":"person-chan","displayName":"陳先生（合成）"},{"isSynthetic":true,"provisional":true,"id":"district-01-hh1-p1","displayName":"演示街坊 01A1","addressNote":"晴里樓（合成） · 1樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-01-hh1-p2","displayName":"演示街坊 01A2","addressNote":"晴里樓（合成） · 1樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-01-hh2-p1","displayName":"演示街坊 01B1","addressNote":"晴里樓（合成） · 1樓 C室（合成）","contactNote":"合成：只保留稱呼，未提供電話；聯絡意願待確認。"},{"isSynthetic":true,"provisional":true,"id":"district-01-hh3-p1","displayName":"演示街坊 01C1","addressNote":"晴里樓（合成） · 2樓 B室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-02-hh1-p1","displayName":"演示街坊 02A1","addressNote":"青禾樓（合成） · 1樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-02-hh1-p2","displayName":"演示街坊 02A2","addressNote":"青禾樓（合成） · 1樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-02-hh2-p1","displayName":"演示街坊 02B1","addressNote":"青禾樓（合成） · 1樓 C室（合成）","contactNote":"合成：只保留稱呼，未提供電話；聯絡意願待確認。"},{"isSynthetic":true,"provisional":true,"id":"district-02-hh3-p1","displayName":"演示街坊 02C1","addressNote":"青禾樓（合成） · 2樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-03-hh1-p1","displayName":"演示街坊 03A1","addressNote":"映榕樓（合成） · 1樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-03-hh1-p2","displayName":"演示街坊 03A2","addressNote":"映榕樓（合成） · 1樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-03-hh2-p1","displayName":"演示街坊 03B1","addressNote":"映榕樓（合成） · 2樓 A室（合成）","contactNote":"合成：只保留稱呼，未提供電話；聯絡意願待確認。"},{"isSynthetic":true,"provisional":true,"id":"district-03-hh3-p1","displayName":"演示街坊 03C1","addressNote":"映榕樓（合成） · 3樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-04-hh1-p1","displayName":"演示街坊 04A1","addressNote":"小滿樓（合成） · 1樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-04-hh1-p2","displayName":"演示街坊 04A2","addressNote":"小滿樓（合成） · 1樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-04-hh2-p1","displayName":"演示街坊 04B1","addressNote":"小滿樓（合成） · 1樓 C室（合成）","contactNote":"合成：只保留稱呼，未提供電話；聯絡意願待確認。"},{"isSynthetic":true,"provisional":true,"id":"district-04-hh3-p1","displayName":"演示街坊 04C1","addressNote":"小滿樓（合成） · 2樓 B室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-05-hh1-p1","displayName":"演示街坊 05A1","addressNote":"常悅樓（合成） · 1樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-05-hh1-p2","displayName":"演示街坊 05A2","addressNote":"常悅樓（合成） · 1樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-05-hh2-p1","displayName":"演示街坊 05B1","addressNote":"常悅樓（合成） · 1樓 C室（合成）","contactNote":"合成：只保留稱呼，未提供電話；聯絡意願待確認。"},{"isSynthetic":true,"provisional":true,"id":"district-05-hh3-p1","displayName":"演示街坊 05C1","addressNote":"常悅樓（合成） · 2樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-06-hh1-p1","displayName":"演示街坊 06A1","addressNote":"知秋樓（合成） · 具體位置待核對（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-06-hh1-p2","displayName":"演示街坊 06A2","addressNote":"知秋樓（合成） · 具體位置待核對（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-06-hh2-p1","displayName":"演示街坊 06B1","addressNote":"知秋樓（合成） · 具體位置待核對（合成）","contactNote":"合成：只保留稱呼，未提供電話；聯絡意願待確認。"},{"isSynthetic":true,"provisional":true,"id":"district-07-hh1-p1","displayName":"演示街坊 07A1","addressNote":"晴川樓（合成） · 1樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-07-hh1-p2","displayName":"演示街坊 07A2","addressNote":"晴川樓（合成） · 1樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-07-hh2-p1","displayName":"演示街坊 07B1","addressNote":"晴川樓（合成） · 2樓 A室（合成）","contactNote":"合成：只保留稱呼，未提供電話；聯絡意願待確認。"},{"isSynthetic":true,"provisional":true,"id":"district-07-hh3-p1","displayName":"演示街坊 07C1","addressNote":"晴川樓（合成） · 3樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-08-hh1-p1","displayName":"演示街坊 08A1","addressNote":"穗安樓（合成） · 1樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-08-hh1-p2","displayName":"演示街坊 08A2","addressNote":"穗安樓（合成） · 1樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-08-hh2-p1","displayName":"演示街坊 08B1","addressNote":"穗安樓（合成） · 1樓 C室（合成）","contactNote":"合成：只保留稱呼，未提供電話；聯絡意願待確認。"},{"isSynthetic":true,"provisional":true,"id":"district-08-hh3-p1","displayName":"演示街坊 08C1","addressNote":"穗安樓（合成） · 2樓 B室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-09-hh1-p1","displayName":"演示街坊 09A1","addressNote":"棠和樓（合成） · 1樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-09-hh1-p2","displayName":"演示街坊 09A2","addressNote":"棠和樓（合成） · 1樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-09-hh2-p1","displayName":"演示街坊 09B1","addressNote":"棠和樓（合成） · 1樓 C室（合成）","contactNote":"合成：只保留稱呼，未提供電話；聯絡意願待確認。"},{"isSynthetic":true,"provisional":true,"id":"district-09-hh3-p1","displayName":"演示街坊 09C1","addressNote":"棠和樓（合成） · 2樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-10-hh1-p1","displayName":"演示街坊 10A1","addressNote":"日和樓（合成） · 1樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-10-hh1-p2","displayName":"演示街坊 10A2","addressNote":"日和樓（合成） · 1樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-10-hh2-p1","displayName":"演示街坊 10B1","addressNote":"日和樓（合成） · 2樓 A室（合成）","contactNote":"合成：只保留稱呼，未提供電話；聯絡意願待確認。"},{"isSynthetic":true,"provisional":true,"id":"district-10-hh3-p1","displayName":"演示街坊 10C1","addressNote":"日和樓（合成） · 3樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-11-hh1-p1","displayName":"演示街坊 11A1","addressNote":"朗月樓（合成） · 1樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-11-hh1-p2","displayName":"演示街坊 11A2","addressNote":"朗月樓（合成） · 1樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-11-hh2-p1","displayName":"演示街坊 11B1","addressNote":"朗月樓（合成） · 1樓 C室（合成）","contactNote":"合成：只保留稱呼，未提供電話；聯絡意願待確認。"},{"isSynthetic":true,"provisional":true,"id":"district-11-hh3-p1","displayName":"演示街坊 11C1","addressNote":"朗月樓（合成） · 2樓 B室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-12-hh1-p1","displayName":"演示街坊 12A1","addressNote":"杏林樓（合成） · 具體位置待核對（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-12-hh1-p2","displayName":"演示街坊 12A2","addressNote":"杏林樓（合成） · 具體位置待核對（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-12-hh2-p1","displayName":"演示街坊 12B1","addressNote":"杏林樓（合成） · 具體位置待核對（合成）","contactNote":"合成：只保留稱呼，未提供電話；聯絡意願待確認。"},{"isSynthetic":true,"provisional":true,"id":"district-13-hh1-p1","displayName":"演示街坊 13A1","addressNote":"拾光樓（合成） · 1樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-13-hh1-p2","displayName":"演示街坊 13A2","addressNote":"拾光樓（合成） · 1樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-13-hh2-p1","displayName":"演示街坊 13B1","addressNote":"拾光樓（合成） · 2樓 A室（合成）","contactNote":"合成：只保留稱呼，未提供電話；聯絡意願待確認。"},{"isSynthetic":true,"provisional":true,"id":"district-13-hh3-p1","displayName":"演示街坊 13C1","addressNote":"拾光樓（合成） · 3樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-15-hh1-p1","displayName":"演示街坊 15A1","addressNote":"榕溪樓（合成） · 1樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-15-hh1-p2","displayName":"演示街坊 15A2","addressNote":"榕溪樓（合成） · 1樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-15-hh2-p1","displayName":"演示街坊 15B1","addressNote":"榕溪樓（合成） · 1樓 C室（合成）","contactNote":"合成：只保留稱呼，未提供電話；聯絡意願待確認。"},{"isSynthetic":true,"provisional":true,"id":"district-15-hh3-p1","displayName":"演示街坊 15C1","addressNote":"榕溪樓（合成） · 2樓 B室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"}],"householdMemberships":[{"isSynthetic":true,"provisional":true,"id":"hhm-lam","householdId":"household-lam","personId":"person-lam","relationship":"戶主（合成）"},{"isSynthetic":true,"provisional":true,"id":"district-01-hh1-p1-household","householdId":"district-01-hh1","personId":"district-01-hh1-p1","relationship":"合成主要聯絡人"},{"isSynthetic":true,"provisional":true,"id":"district-01-hh1-p2-household","householdId":"district-01-hh1","personId":"district-01-hh1-p2","relationship":"合成同住成員"},{"isSynthetic":true,"provisional":true,"id":"district-01-hh2-p1-household","householdId":"district-01-hh2","personId":"district-01-hh2-p1","relationship":"合成主要聯絡人"},{"isSynthetic":true,"provisional":true,"id":"district-01-hh3-p1-household","householdId":"district-01-hh3","personId":"district-01-hh3-p1","relationship":"合成主要聯絡人"},{"isSynthetic":true,"provisional":true,"id":"district-02-hh1-p1-household","householdId":"district-02-hh1","personId":"district-02-hh1-p1","relationship":"合成主要聯絡人"},{"isSynthetic":true,"provisional":true,"id":"district-02-hh1-p2-household","householdId":"district-02-hh1","personId":"district-02-hh1-p2","relationship":"合成同住成員"},{"isSynthetic":true,"provisional":true,"id":"district-02-hh2-p1-house</x:v>
+        <x:v>rage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-13-f4-B","buildingId":"district-13","floorId":"district-13-f4","label":"4樓 B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-13-f5-A","buildingId":"district-13","floorId":"district-13-f5","label":"5樓 A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-13-f5-B","buildingId":"district-13","floorId":"district-13-f5","label":"5樓 B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-13-f6-A","buildingId":"district-13","floorId":"district-13-f6","label":"6樓 A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-13-f6-B","buildingId":"district-13","floorId":"district-13-f6","label":"6樓 B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-13-f7-A","buildingId":"district-13","floorId":"district-13-f7","label":"7樓 A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-13-f7-B","buildingId":"district-13","floorId":"district-13-f7","label":"7樓 B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-13-f8-A","buildingId":"district-13","floorId":"district-13-f8","label":"8樓 A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-13-f8-B","buildingId":"district-13","floorId":"district-13-f8","label":"8樓 B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-13-f9-A","buildingId":"district-13","floorId":"district-13-f9","label":"9樓 A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-13-f9-B","buildingId":"district-13","floorId":"district-13-f9","label":"9樓 B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-13-f10-A","buildingId":"district-13","floorId":"district-13-f10","label":"10樓 A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-13-f10-B","buildingId":"district-13","floorId":"district-13-f10","label":"10樓 B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-13-f11-A","buildingId":"district-13","floorId":"district-13-f11","label":"11樓 A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-13-f11-B","buildingId":"district-13","floorId":"district-13-f11","label":"11樓 B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-13-f12-A","buildingId":"district-13","floorId":"district-13-f12","label":"12樓 A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-13-f12-B","buildingId":"district-13","floorId":"district-13-f12","label":"12樓 B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-13-f13-A","buildingId":"district-13","floorId":"district-13-f13","label":"13樓 A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-13-f13-B","buildingId":"district-13","floorId":"district-13-f13","label":"13樓 B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-14-f1-A","buildingId":"district-14","floorId":"district-14-f1","label":"1樓 A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-14-f1-B","buildingId":"district-14","floorId":"district-14-f1","label":"1樓 B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-14-f1-C","buildingId":"district-14","floorId":"district-14-f1","label":"1樓 C室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-14-f1-D","buildingId":"district-14","floorId":"district-14-f1","label":"1樓 D室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-14-f2-A","buildingId":"district-14","floorId":"district-14-f2","label":"2樓 A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-14-f2-B","buildingId":"district-14","floorId":"district-14-f2","label":"2樓 B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-14-f2-C","buildingId":"district-14","floorId":"district-14-f2","label":"2樓 C室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-14-f2-D","buildingId":"district-14","floorId":"district-14-f2","label":"2樓 D室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-14-f3-A","buildingId":"district-14","floorId":"district-14-f3","label":"3樓 A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-14-f3-B","buildingId":"district-14","floorId":"district-14-f3","label":"3樓 B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-14-f3-C","buildingId":"district-14","floorId":"district-14-f3","label":"3樓 C室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-14-f3-D","buildingId":"district-14","floorId":"district-14-f3","label":"3樓 D室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-14-f4-A","buildingId":"district-14","floorId":"district-14-f4","label":"4樓 A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-14-f4-B","buildingId":"district-14","floorId":"district-14-f4","label":"4樓 B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-14-f4-C","buildingId":"district-14","floorId":"district-14-f4","label":"4樓 C室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-14-f4-D","buildingId":"district-14","floorId":"district-14-f4","label":"4樓 D室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-14-f5-A","buildingId":"district-14","floorId":"district-14-f5","label":"5樓 A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-14-f5-B","buildingId":"district-14","floorId":"district-14-f5","label":"5樓 B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-14-f5-C","buildingId":"district-14","floorId":"district-14-f5","label":"5樓 C室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-14-f5-D","buildingId":"district-14","floorId":"district-14-f5","label":"5樓 D室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-14-f6-A","buildingId":"district-14","floorId":"district-14-f6","label":"6樓 A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-14-f6-B","buildingId":"district-14","floorId":"district-14-f6","label":"6樓 B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-14-f6-C","buildingId":"district-14","floorId":"district-14-f6","label":"6樓 C室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-14-f6-D","buildingId":"district-14","floorId":"district-14-f6","label":"6樓 D室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-15-f1-A","buildingId":"district-15","floorId":"district-15-f1","label":"1樓 A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-15-f1-B","buildingId":"district-15","floorId":"district-15-f1","label":"1樓 B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-15-f1-C","buildingId":"district-15","floorId":"district-15-f1","label":"1樓 C室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-15-f2-A","buildingId":"district-15","floorId":"district-15-f2","label":"2樓 A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-15-f2-B","buildingId":"district-15","floorId":"district-15-f2","label":"2樓 B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-15-f2-C","buildingId":"district-15","floorId":"district-15-f2","label":"2樓 C室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-15-f3-A","buildingId":"district-15","floorId":"district-15-f3","label":"3樓 A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-15-f3-B","buildingId":"district-15","floorId":"district-15-f3","label":"3樓 B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-15-f3-C","buildingId":"district-15","floorId":"district-15-f3","label":"3樓 C室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-15-f4-A","buildingId":"district-15","floorId":"district-15-f4","label":"4樓 A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-15-f4-B","buildingId":"district-15","floorId":"district-15-f4","label":"4樓 B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-15-f4-C","buildingId":"district-15","floorId":"district-15-f4","label":"4樓 C室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-15-f5-A","buildingId":"district-15","floorId":"district-15-f5","label":"5樓 A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-15-f5-B","buildingId":"district-15","floorId":"district-15-f5","label":"5樓 B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-15-f5-C","buildingId":"district-15","floorId":"district-15-f5","label":"5樓 C室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-15-f6-A","buildingId":"district-15","floorId":"district-15-f6","label":"6樓 A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-15-f6-B","buildingId":"district-15","floorId":"district-15-f6","label":"6樓 B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-15-f6-C","buildingId":"district-15","floorId":"district-15-f6","label":"6樓 C室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-15-f7-A","buildingId":"district-15","floorId":"district-15-f7","label":"7樓 A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-15-f7-B","buildingId":"district-15","floorId":"district-15-f7","label":"7樓 B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-15-f7-C","buildingId":"district-15","floorId":"district-15-f7","label":"7樓 C室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-15-f8-A","buildingId":"district-15","floorId":"district-15-f8","label":"8樓 A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-15-f8-B","buildingId":"district-15","floorId":"district-15-f8","label":"8樓 B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-15-f8-C","buildingId":"district-15","floorId":"district-15-f8","label":"8樓 C室","initialCoverage":"UNVISITED"}],"households":[{"isSynthetic":true,"provisional":true,"id":"household-lam","label":"林家庭（合成）"},{"isSynthetic":true,"provisional":true,"id":"district-01-hh1","label":"合成家庭 01-1"},{"isSynthetic":true,"provisional":true,"id":"district-01-hh2","label":"合成家庭 01-2"},{"isSynthetic":true,"provisional":true,"id":"district-01-hh3","label":"合成家庭 01-3"},{"isSynthetic":true,"provisional":true,"id":"district-02-hh1","label":"合成家庭 02-1"},{"isSynthetic":true,"provisional":true,"id":"district-02-hh2","label":"合成家庭 02-2"},{"isSynthetic":true,"provisional":true,"id":"district-02-hh3","label":"合成家庭 02-3"},{"isSynthetic":true,"provisional":true,"id":"district-03-hh1","label":"合成家庭 03-1"},{"isSynthetic":true,"provisional":true,"id":"district-03-hh2","label":"合成家庭 03-2"},{"isSynthetic":true,"provisional":true,"id":"district-03-hh3","label":"合成家庭 03-3"},{"isSynthetic":true,"provisional":true,"id":"district-04-hh1","label":"合成家庭 04-1"},{"isSynthetic":true,"provisional":true,"id":"district-04-hh2","label":"合成家庭 04-2"},{"isSynthetic":true,"provisional":true,"id":"district-04-hh3","label":"合成家庭 04-3"},{"isSynthetic":true,"provisional":true,"id":"district-05-hh1","label":"合成家庭 05-1"},{"isSynthetic":true,"provisional":true,"id":"district-05-hh2","label":"合成家庭 05-2"},{"isSynthetic":true,"provisional":true,"id":"district-05-hh3","label":"合成家庭 05-3"},{"isSynthetic":true,"provisional":true,"id":"district-06-hh1","label":"合成家庭 06-1"},{"isSynthetic":true,"provisional":true,"id":"district-06-hh2","label":"合成家庭 06-2"},{"isSynthetic":true,"provisional":true,"id":"district-07-hh1","label":"合成家庭 07-1"},{"isSynthetic":true,"provisional":true,"id":"district-07-hh2","label":"合成家庭 07-2"},{"isSynthetic":true,"provisional":true,"id":"district-07-hh3","label":"合成家庭 07-3"},{"isSynthetic":true,"provisional":true,"id":"district-08-hh1","label":"合成家庭 08-1"},{"isSynthetic":true,"provisional":true,"id":"district-08-hh2","label":"合成家庭 08-2"},{"isSynthetic":true,"provisional":true,"id":"district-08-hh3","label":"合成家庭 08-3"},{"isSynthetic":true,"provisional":true,"id":"district-09-hh1","label":"合成家庭 09-1"},{"isSynthetic":true,"provisional":true,"id":"district-09-hh2","label":"合成家庭 09-2"},{"isSynthetic":true,"provisional":true,"id":"district-09-hh3","label":"合成家庭 09-3"},{"isSynthetic":true,"provisional":true,"id":"district-10-hh1","label":"合成家庭 10-1"},{"isSynthetic":true,"provisional":true,"id":"district-10-hh2","label":"合成家庭 10-2"},{"isSynthetic":true,"provisional":true,"id":"district-10-hh3","label":"合成家庭 10-3"},{"isSynthetic":true,"provisional":true,"id":"district-11-hh1","label":"合成家庭 11-1"},{"isSynthetic":true,"provisional":true,"id":"district-11-hh2","label":"合成家庭 11-2"},{"isSynthetic":true,"provisional":true,"id":"district-11-hh3","label":"合成家庭 11-3"},{"isSynthetic":true,"provisional":true,"id":"district-12-hh1","label":"合成家庭 12-1"},{"isSynthetic":true,"provisional":true,"id":"district-12-hh2","label":"合成家庭 12-2"},{"isSynthetic":true,"provisional":true,"id":"district-13-hh1","label":"合成家庭 13-1"},{"isSynthetic":true,"provisional":true,"id":"district-13-hh2","label":"合成家庭 13-2"},{"isSynthetic":true,"provisional":true,"id":"district-13-hh3","label":"合成家庭 13-3"},{"isSynthetic":true,"provisional":true,"id":"district-15-hh1","label":"合成家庭 15-1"},{"isSynthetic":true,"provisional":true,"id":"district-15-hh2","label":"合成家庭 15-2"},{"isSynthetic":true,"provisional":true,"id":"district-15-hh3","label":"合成家庭 15-3"}],"people":[{"isSynthetic":true,"provisional":true,"id":"person-lam","displayName":"林女士（合成）"},{"isSynthetic":true,"provisional":true,"id":"person-chan","displayName":"陳先生（合成）"},{"isSynthetic":true,"provisional":true,"id":"district-01-hh1-p1","displayName":"演示街坊 01A1","addressNote":"晴里樓 · 1樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-01-hh1-p2","displayName":"演示街坊 01A2","addressNote":"晴里樓 · 1樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-01-hh2-p1","displayName":"演示街坊 01B1","addressNote":"晴里樓 · 1樓 C室（合成）","contactNote":"合成：只保留稱呼，未提供電話；聯絡意願待確認。"},{"isSynthetic":true,"provisional":true,"id":"district-01-hh3-p1","displayName":"演示街坊 01C1","addressNote":"晴里樓 · 2樓 B室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-02-hh1-p1","displayName":"演示街坊 02A1","addressNote":"青禾樓 · 1樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-02-hh1-p2","displayName":"演示街坊 02A2","addressNote":"青禾樓 · 1樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-02-hh2-p1","displayName":"演示街坊 02B1","addressNote":"青禾樓 · 1樓 C室（合成）","contactNote":"合成：只保留稱呼，未提供電話；聯絡意願待確認。"},{"isSynthetic":true,"provisional":true,"id":"district-02-hh3-p1","displayName":"演示街坊 02C1","addressNote":"青禾樓 · 2樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-03-hh1-p1","displayName":"演示街坊 03A1","addressNote":"映榕樓 · 1樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-03-hh1-p2","displayName":"演示街坊 03A2","addressNote":"映榕樓 · 1樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-03-hh2-p1","displayName":"演示街坊 03B1","addressNote":"映榕樓 · 2樓 A室（合成）","contactNote":"合成：只保留稱呼，未提供電話；聯絡意願待確認。"},{"isSynthetic":true,"provisional":true,"id":"district-03-hh3-p1","displayName":"演示街坊 03C1","addressNote":"映榕樓 · 3樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-04-hh1-p1","displayName":"演示街坊 04A1","addressNote":"小滿樓 · 1樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-04-hh1-p2","displayName":"演示街坊 04A2","addressNote":"小滿樓 · 1樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-04-hh2-p1","displayName":"演示街坊 04B1","addressNote":"小滿樓 · 1樓 C室（合成）","contactNote":"合成：只保留稱呼，未提供電話；聯絡意願待確認。"},{"isSynthetic":true,"provisional":true,"id":"district-04-hh3-p1","displayName":"演示街坊 04C1","addressNote":"小滿樓 · 2樓 B室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-05-hh1-p1","displayName":"演示街坊 05A1","addressNote":"常悅樓 · 1樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-05-hh1-p2","displayName":"演示街坊 05A2","addressNote":"常悅樓 · 1樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-05-hh2-p1","displayName":"演示街坊 05B1","addressNote":"常悅樓 · 1樓 C室（合成）","contactNote":"合成：只保留稱呼，未提供電話；聯絡意願待確認。"},{"isSynthetic":true,"provisional":true,"id":"district-05-hh3-p1","displayName":"演示街坊 05C1","addressNote":"常悅樓 · 2樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-06-hh1-p1","displayName":"演示街坊 06A1","addressNote":"知秋樓 · 具體位置待核對（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-06-hh1-p2","displayName":"演示街坊 06A2","addressNote":"知秋樓 · 具體位置待核對（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-06-hh2-p1","displayName":"演示街坊 06B1","addressNote":"知秋樓 · 具體位置待核對（合成）","contactNote":"合成：只保留稱呼，未提供電話；聯絡意願待確認。"},{"isSynthetic":true,"provisional":true,"id":"district-07-hh1-p1","displayName":"演示街坊 07A1","addressNote":"晴川樓 · 1樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-07-hh1-p2","displayName":"演示街坊 07A2","addressNote":"晴川樓 · 1樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-07-hh2-p1","displayName":"演示街坊 07B1","addressNote":"晴川樓 · 2樓 A室（合成）","contactNote":"合成：只保留稱呼，未提供電話；聯絡意願待確認。"},{"isSynthetic":true,"provisional":true,"id":"district-07-hh3-p1","displayName":"演示街坊 07C1","addressNote":"晴川樓 · 3樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-08-hh1-p1","displayName":"演示街坊 08A1","addressNote":"穗安樓 · 1樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-08-hh1-p2","displayName":"演示街坊 08A2","addressNote":"穗安樓 · 1樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-08-hh2-p1","displayName":"演示街坊 08B1","addressNote":"穗安樓 · 1樓 C室（合成）","contactNote":"合成：只保留稱呼，未提供電話；聯絡意願待確認。"},{"isSynthetic":true,"provisional":true,"id":"district-08-hh3-p1","displayName":"演示街坊 08C1","addressNote":"穗安樓 · 2樓 B室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-09-hh1-p1","displayName":"演示街坊 09A1","addressNote":"棠和樓 · 1樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-09-hh1-p2","displayName":"演示街坊 09A2","addressNote":"棠和樓 · 1樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-09-hh2-p1","displayName":"演示街坊 09B1","addressNote":"棠和樓 · 1樓 C室（合成）","contactNote":"合成：只保留稱呼，未提供電話；聯絡意願待確認。"},{"isSynthetic":true,"provisional":true,"id":"district-09-hh3-p1","displayName":"演示街坊 09C1","addressNote":"棠和樓 · 2樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-10-hh1-p1","displayName":"演示街坊 10A1","addressNote":"日和樓 · 1樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-10-hh1-p2","displayName":"演示街坊 10A2","addressNote":"日和樓 · 1樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-10-hh2-p1","displayName":"演示街坊 10B1","addressNote":"日和樓 · 2樓 A室（合成）","contactNote":"合成：只保留稱呼，未提供電話；聯絡意願待確認。"},{"isSynthetic":true,"provisional":true,"id":"district-10-hh3-p1","displayName":"演示街坊 10C1","addressNote":"日和樓 · 3樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-11-hh1-p1","displayName":"演示街坊 11A1","addressNote":"朗月樓 · 1樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-11-hh1-p2","displayName":"演示街坊 11A2","addressNote":"朗月樓 · 1樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-11-hh2-p1","displayName":"演示街坊 11B1","addressNote":"朗月樓 · 1樓 C室（合成）","contactNote":"合成：只保留稱呼，未提供電話；聯絡意願待確認。"},{"isSynthetic":true,"provisional":true,"id":"district-11-hh3-p1","displayName":"演示街坊 11C1","addressNote":"朗月樓 · 2樓 B室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-12-hh1-p1","displayName":"演示街坊 12A1","addressNote":"杏林樓 · 具體位置待核對（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-12-hh1-p2","displayName":"演示街坊 12A2","addressNote":"杏林樓 · 具體位置待核對（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-12-hh2-p1","displayName":"演示街坊 12B1","addressNote":"杏林樓 · 具體位置待核對（合成）","contactNote":"合成：只保留稱呼，未提供電話；聯絡意願待確認。"},{"isSynthetic":true,"provisional":true,"id":"district-13-hh1-p1","displayName":"演示街坊 13A1","addressNote":"拾光樓 · 1樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-13-hh1-p2","displayName":"演示街坊 13A2","addressNote":"拾光樓 · 1樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-13-hh2-p1","displayName":"演示街坊 13B1","addressNote":"拾光樓 · 2樓 A室（合成）","contactNote":"合成：只保留稱呼，未提供電話；聯絡意願待確認。"},{"isSynthetic":true,"provisional":true,"id":"district-13-hh3-p1","displayName":"演示街坊 13C1","addressNote":"拾光樓 · 3樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-15-hh1-p1","displayName":"演示街坊 15A1","addressNote":"榕溪樓 · 1樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-15-hh1-p2","displayName":"演示街坊 15A2","addressNote":"榕溪樓 · 1樓 A室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"},{"isSynthetic":true,"provisional":true,"id":"district-15-hh2-p1","displayName":"演示街坊 15B1","addressNote":"榕溪樓 · 1樓 C室（合成）","contactNote":"合成：只保留稱呼，未提供電話；聯絡意願待確認。"},{"isSynthetic":true,"provisional":true,"id":"district-15-hh3-p1","displayName":"演示街坊 15C1","addressNote":"榕溪樓 · 2樓 B室（合成）","contactNote":"合成：演示名冊記錄，不含真實姓名、電話或個人資料。"}],"householdMemberships":[{"isSynthetic":true,"provisional":true,"id":"hhm-lam","householdId":"household-lam","personId":"person-lam","relationship":"戶主（合成）"},{"isSynthetic":true,"provisional":true,"id":"district-01-hh1-p1-household","householdId":"district-01-hh1","personId":"district-01-hh1-p1","relationship":"合成主要聯絡人"},{"isSynthetic":true,"provisional":true,"id":"district-01-hh1-p2-household","householdId":"district-01-hh1","personId":"district-01-hh1-p2","relationship":"合成同住成員"},{"isSynthetic":true,"provisional":true,"id":"district-01-hh2-p1-household","householdId":"district-01-hh2","personId":"district-01-hh2-p1","relationship":"合成主要聯絡人"},{"isSynthetic":true,"provisional":true,"id":"district-01-hh3-p1-household","householdId":"district-01-hh3","personId":"district-01-hh3-p1","relationship":"合成主要聯絡人"},{"isSynthetic":true,"provisional":true,"id":"district-02-hh1-p1-household","householdId":"district-02-hh1","personId":"district-02-hh1-p1","relationship":"合成主要聯絡人"},{"isSynthetic":true,"provisional":true,"id":"district-02-hh1-p2-household","householdId":"district-02-hh1","personId":"district-02-hh1-p2","relationship":"合成同住成員"},{"isSynthetic":true,"provisional":true,"id":"district-02-hh2-p1-house</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="25" customHeight="1">

--- a/public/demo/careflow-district-demo.xlsx
+++ b/public/demo/careflow-district-demo.xlsx
@@ -784,7 +784,7 @@
         <x:v>裕安樓</x:v>
       </x:c>
       <x:c r="C7" s="12" t="str">
-        <x:v>西營盤示範街 1 號（合成）</x:v>
+        <x:v>西營盤示範街 1 號</x:v>
       </x:c>
       <x:c r="D7" s="10" t="str">
         <x:v>1F：1F A室、1F B室、1F C室、1F D室
@@ -820,7 +820,7 @@
         <x:v>海景樓</x:v>
       </x:c>
       <x:c r="C8" s="13" t="str">
-        <x:v>西營盤示範街 8 號（合成）</x:v>
+        <x:v>西營盤示範街 8 號</x:v>
       </x:c>
       <x:c r="D8" s="11" t="str">
         <x:v>1F：1F A室、1F B室
@@ -850,7 +850,7 @@
         <x:v>德昌樓</x:v>
       </x:c>
       <x:c r="C9" s="12" t="str">
-        <x:v>西營盤示範街 16 號（合成）</x:v>
+        <x:v>西營盤示範街 16 號</x:v>
       </x:c>
       <x:c r="D9" s="10" t="str">
         <x:v>樓層／單位未核實</x:v>
@@ -879,7 +879,7 @@
         <x:v>安和樓</x:v>
       </x:c>
       <x:c r="C10" s="13" t="str">
-        <x:v>西營盤示範街 24 號（合成）</x:v>
+        <x:v>西營盤示範街 24 號</x:v>
       </x:c>
       <x:c r="D10" s="11" t="str">
         <x:v>樓層／單位未核實</x:v>
@@ -1560,7 +1560,7 @@
       </x:c>
       <x:c r="C7" s="18" t="str"/>
       <x:c r="D7" s="12" t="str">
-        <x:v>西營盤示範街 1 號（合成） 5F B室</x:v>
+        <x:v>西營盤示範街 1 號 5F B室</x:v>
       </x:c>
       <x:c r="E7" s="12" t="str"/>
       <x:c r="F7" s="10" t="str">
@@ -19221,7 +19221,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B7" s="37" t="str">
-        <x:v>{"schemaVersion":"0.1-demo","isSynthetic":true,"notice":"全區合成演示：20 個大廈位置用作介面測試；樓名、地址、樓層、單位、住戶及記錄均屬虛構，不代表地圖底圖中的真實建築或居民。依原紙本＋Excel 工作流設計，欄位仍待機構確認。","buildings":[{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an","name":"裕安樓","address":"西營盤示範街 1 號（合成）","layoutDeclared":true,"floorCount":8,"initialCoverage":"UNVISITED","coordinates":{"lng":114.14178818464279,"lat":22.286363930711317},"footprint":[[114.14168894290924,22.286500432351488],[114.1418981552124,22.286495468660235],[114.14189279079437,22.286227429071147],[114.14167821407318,22.286237356472498],[114.14168894290924,22.286500432351488]]},{"isSynthetic":true,"provisional":true,"id":"bldg-hoi-king","name":"海景樓","address":"西營盤示範街 8 號（合成）","layoutDeclared":true,"floorCount":2,"initialCoverage":"UNVISITED","coordinates":{"lng":114.14255797863007,"lat":22.28661211534631},"footprint":[[114.14262235164642,22.286664234063778],[114.14262235164642,22.286619560888553],[114.14259016513824,22.286624524575387],[114.14258480072021,22.286589778763798],[114.14263308048248,22.286589778763798],[114.14263308048248,22.286555032943582],[114.14248287677765,22.286559996632704],[114.14248287677765,22.28659474245171],[114.14253115653992,22.28659474245171],[114.14253115653992,22.286624524575387],[114.14249897003174,22.286624524575387],[114.14249897003174,22.286669197749035],[114.14262235164642,22.286664234063778]]},{"isSynthetic":true,"provisional":true,"id":"bldg-duk-cheong","name":"德昌樓","address":"西營盤示範街 16 號（合成）","layoutDeclared":false,"initialCoverage":"UNKNOWN","coordinates":{"lng":114.14136976003647,"lat":22.286808180844794},"footprint":[[114.1414475440979,22.286733725641312],[114.14129197597504,22.286733725641312],[114.14129197597504,22.286882636048276],[114.1414475440979,22.286877672370593],[114.1414475440979,22.286733725641312]]},{"isSynthetic":true,"provisional":true,"id":"bldg-on-wo","name":"安和樓","address":"西營盤示範街 24 號（合成）","layoutDeclared":false,"initialCoverage":"UNKNOWN","coordinates":{"lng":114.14208590984344,"lat":22.28576580411479},"footprint":[[114.14213418960571,22.285825368723906],[114.14212882518768,22.28570127579063],[114.14203763008118,22.285706239510063],[114.1420429944992,22.285830332438948],[114.14213418960571,22.285825368723906]]},{"isSynthetic":true,"provisional":true,"id":"district-01","name":"晴里樓","address":"演示街區 01 號 · 虛構地址","coordinates":{"lng":114.13954049348831,"lat":22.287835658837054},"footprint":[[114.13945734500885,22.287890258967195],[114.13946807384491,22.287865440755937],[114.13947880268097,22.28787040439856],[114.13946270942688,22.287920040814882],[114.1395378112793,22.287939895376482],[114.13955390453339,22.287890258967195],[114.13956463336945,22.287890258967195],[114.13954854011536,22.287944859016434],[114.13962364196777,22.28796471357451],[114.13963973522186,22.287910113533016],[114.13965582847595,22.28791507717405],[114.13966655731201,22.28787536804097],[114.13965046405792,22.28787040439856],[114.13966119289398,22.287835658896626],[114.1396826505661,22.287840622540287],[114.13970410823822,22.28778105880474],[114.13943588733673,22.287706604099597],[114.1393768787384,22.28789522260891],[114.13945198059082,22.28791507717405],[114.13945734500885,22.287890258967195]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":10},{"isSynthetic":true,"provisional":true,"id":"district-02","name":"青禾樓","address":"演示街區 02 號 · 虛構地址","coordinates":{"lng":114.14060264825821,"lat":22.287644558357755},"footprint":[[114.14048731327057,22.28780091338608],[114.14061069488525,22.28783069525278],[114.14062678813934,22.28778105880474],[114.1406911611557,22.287795949740996],[114.14071798324585,22.287696676802582],[114.14065897464752,22.28768178585574],[114.14071261882782,22.28749316705843],[114.1405838727951,22.28745842146273],[114.14048731327057,22.28780091338608]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":7},{"isSynthetic":true,"provisional":true,"id":"district-03","name":"映榕樓","address":"演示街區 03 號 · 虛構地址","coordinates":{"lng":114.14200276136398,"lat":22.287753758732258},"footprint":[[114.14189279079437,22.287686749504857],[114.1418981552124,22.287825731608777],[114.1421127319336,22.28782076796459],[114.14210736751556,22.28768178585574],[114.14189279079437,22.287686749504857]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":12},{"isSynthetic":true,"provisional":true,"id":"district-04","name":"小滿樓","address":"演示街區 04 號 · 虛構地址","coordinates":{"lng":114.14324462413788,"lat":22.287714049553372},"footprint":[[114.14331436157227,22.28778105880474],[114.14330899715424,22.28764207665641],[114.14319097995758,22.287647040306936],[114.14319097995758,22.287751276927438],[114.14317488670349,22.287751276927438],[114.14317488670349,22.287786022450334],[114.14331436157227,22.28778105880474]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":5},{"isSynthetic":true,"provisional":true,"id":"district-05","name":"常悅樓","address":"演示街區 05 號 · 虛構地址","coordinates":{"lng":114.13936883211136,"lat":22.286842926596464},"footprint":[[114.13924276828766,22.28687270869274],[114.13945734500885,22.286927309139443],[114.13949489593506,22.286818108224736],[114.13928031921387,22.286758544053484],[114.13924276828766,22.28687270869274]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":9},{"isSynthetic":true,"provisional":true,"id":"district-06","name":"知秋樓","address":"演示街區 06 號 · 虛構地址","coordinates":{"lng":114.14092719554901,"lat":22.286840444772693},"footprint":[[114.14082527160645,22.28683796294284],[114.14087355136871,22.28683796294284],[114.14087355136871,22.2868925634031],[114.14098620414734,22.286887599725773],[114.14098620414734,22.28683299926358],[114.14102911949158,22.28683299926358],[114.14102911949158,22.286788326142286],[114.14082527160645,22.286793289823123],[114.14082527160645,22.28683796294284]],"layoutDeclared":false,"initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-07","name":"晴川樓","address":"演示街區 07 號 · 虛構地址","coordinates":{"lng":114.14216101169586,"lat":22.286723798239954},"footprint":[[114.14209127426147,22.286624524575387],[114.14209127426147,22.28665430669274],[114.14210200309753,22.28665430669274],[114.14210736751556,22.286793289823123],[114.1420966386795,22.286793289823123],[114.1420966386795,22.28682307190452],[114.14218246936798,22.28682307190452],[114.14217174053192,22.286763507735387],[114.14223074913025,22.286763507735387],[114.14223074913025,22.286674161434107],[114.14217174053192,22.286674161434107],[114.14217710494995,22.286624524575387],[114.14209127426147,22.286624524575387]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":14},{"isSynthetic":true,"provisional":true,"id":"district-08","name":"穗安樓","address":"演示街區 08 號 · 虛構地址","coordinates":{"lng":114.14348870515823,"lat":22.286728761932885},"footprint":[[114.14357721805573,22.286644379321004],[114.14339482784271,22.286649343006957],[114.14340019226074,22.286813144544766],[114.14358258247375,22.286808180864625],[114.14357721805573,22.286644379321004]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":6},{"isSynthetic":true,"provisional":true,"id":"district-09","name":"棠和樓","address":"演示街區 09 號 · 虛構地址","coordinates":{"lng":114.13955926895142,"lat":22.28589237884831},"footprint":[[114.13951098918915,22.28595442525767],[114.13961291313171,22.28594449783624],[114.13961291313171,22.28592960670275],[114.13965046405792,22.285924642991233],[114.13964509963989,22.285879969579653],[114.13960754871368,22.28588493329275],[114.13960218429565,22.285830332438948],[114.13955926895142,22.28583529615382],[114.13956463336945,22.285870042152922],[114.13954317569733,22.285870042152922],[114.13954317569733,22.28583529615382],[114.13950026035309,22.285840259868493],[114.13950562477112,22.285894860718443],[114.13946807384491,22.285894860718443],[114.13947343826294,22.285939534125234],[114.13951098918915,22.285939534125234],[114.13951098918915,22.28595442525767]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":8},{"isSynthetic":true,"provisional":true,"id":"district-10","name":"日和樓","address":"演示街區 10 號 · 虛構地址","coordinates":{"lng":114.14058923721313,"lat":22.285837777977676},"footprint":[[114.1406375169754,22.285899824431013],[114.14064824581146,22.285899824431013],[114.14064288139343,22.28576580412968],[114.1406375169754,22.28576580412968],[114.14063215255737,22.285740985541267],[114.14057850837708,22.285745949259294],[114.14057850837708,22.285775731563803],[114.14056777954102,22.285775731563803],[114.14056241512299,22.285800550146064],[114.14053022861481,22.285800550146064],[114.14053022861481,22.285855151011503],[114.1405463218689,22.285855151011503],[114.1405463218689,22.285875005866373],[114.14053022861481,22.285875005866373],[114.14053559303284,22.285924642991233],[114.14062142372131,22.285934570414085],[114.14062142372131,22.28592960670275],[114.1406375169754,22.28592960670275],[114.1406375169754,22.285899824431013]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":4},{"isSynthetic":true,"provisional":true,"id":"district-11","name":"朗月樓","address":"演示街區 11 號 · 虛構地址","coordinates":{"lng":114.14172112941742,"lat":22.285909751848486},"footprint":[[114.14187133312225,22.2858650784393],[114.14156556129456,22.285875005866373],[114.14156556129456,22.28595442525767],[114.14187669754028,22.28594449783624],[114.14187133312225,22.2858650784393]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":11},{"isSynthetic":true,"provisional":true,"id":"district-12","name":"杏林樓","address":"演示街區 12 號 · 虛構地址","coordinates":{"lng":114.14298176765442,"lat":22.285726094375427},"footprint":[[114.14291203022003,22.28575091297715],[114.14291203022003,22.285780695280607],[114.14305686950684,22.285775731563803],[114.14305686950684,22.285671493470247],[114.142906665802,22.28567645719076],[114.14291203022003,22.28575091297715]],"layoutDeclared":false,"initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-13","name":"拾光樓","address":"演示街區 13 號 · 虛構地址","coordinates":{"lng":114.13944393396378,"lat":22.284753202106018},"footprint":[[114.13941442966461,22.284693637093838],[114.13939833641052,22.284693637093838],[114.13935005664825,22.284668818315083],[114.13934469223022,22.284678745827122],[114.13930177688599,22.28465392704571],[114.13926959037781,22.2847184558682],[114.13938224315643,22.284768093403684],[114.13938760757446,22.284852477173544],[114.13942515850067,22.284847513423784],[114.13942515850067,22.284857440923133],[114.13946807384491,22.284857440923133],[114.13946270942688,22.284847513423784],[114.13950026035309,22.284842549673854],[114.13949489593506,22.284768093403684],[114.13961827754974,22.284698600849055],[114.13958609104156,22.2846489632889],[114.13954317569733,22.284668818315083],[114.1395378112793,22.284658890802348],[114.13947880268097,22.284688673338437],[114.13946270942688,22.284693637093838],[114.13946270942688,22.284673782071195],[114.13940906524658,22.284673782071195],[114.13941442966461,22.284693637093838]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":13},{"isSynthetic":true,"provisional":true,"id":"district-14","name":"和煦樓","address":"演示街區 14 號 · 虛構地址","coordinates":{"lng":114.14081990718842,"lat":22.284790430151403},"footprint":[[114.14072871208191,22.284604289469698],[114.14073944091797,22.28498649835042],[114.14082527160645,22.284981534605436],[114.14082527160645,22.28496664336936],[114.14091110229492,22.28496664336936],[114.14090037345886,22.284594361952387],[114.14087355136871,22.284594361952387],[114.14087355136871,22.284604289469698],[114.14072871208191,22.284604289469698]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":6},{"isSynthetic":true,"provisional":true,"id":"district-15","name":"榕溪樓","address":"演示街區 15 號 · 虛構地址","coordinates":{"lng":114.1420429944992,"lat":22.284894669027736},"footprint":[[114.14195716381073,22.284951752131732],[114.14212882518768,22.284946788385483],[114.14212346076965,22.28483758592374],[114.142005443573,22.28483758592374],[114.142005443573,22.284877295919713],[114.14195716381073,22.284882259668407],[114.14195716381073,22.284951752131732]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":8},{"isSynthetic":true,"provisional":true,"id":"district-16","name":"微光樓","address":"演示街區 16 號 · 虛構地址","coordinates":{"lng":114.14333045482635,"lat":22.284941824574837},"footprint":[[114.14327681064606,22.285075845730304],[114.14339482784271,22.285070881988474],[114.14337873458862,22.28480780341937],[114.14326608181,22.284812767170536],[114.14327681064606,22.285075845730304]],"layoutDeclared":false,"initialCoverage":"UNKNOWN"}],"floors":[{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f1","buildingId":"bldg-yu-an","label":"1F","level":1},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f2","buildingId":"bldg-yu-an","label":"2F","level":2},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f3","buildingId":"bldg-yu-an","label":"3F","level":3},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f4","buildingId":"bldg-yu-an","label":"4F","level":4},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f5","buildingId":"bldg-yu-an","label":"5F","level":5},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f6","buildingId":"bldg-yu-an","label":"6F","level":6},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f7","buildingId":"bldg-yu-an","label":"7F","level":7},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f8","buildingId":"bldg-yu-an","label":"8F","level":8},{"isSynthetic":true,"provisional":true,"id":"bldg-hoi-king-f1","buildingId":"bldg-hoi-king","label":"1F","level":1},{"isSynthetic":true,"provisional":true,"id":"bldg-hoi-king-f2","buildingId":"bldg-hoi-king","label":"2F","level":2},{"isSynthetic":true,"provisional":true,"id":"district-01-f1","buildingId":"district-01","level":1,"label":"1 樓"},{"isSynthetic":true,"provisional":true,"id":"district-01-f2","buildingId":"district-01","level":2,"label":"2 樓"},{"isSynthetic":true,"provisional":true,"id":"district-01-f3","buildingId":"district-01","level":3,"label":"3 樓"},{"isSynthetic":true,"provisional":true,"id":"district-01-f4","buildingId":"district-01","level":4,"label":"4 樓"},{"isSynthetic":true,"provisional":true,"id":"district-01-f5","buildingId":"district-01","level":5,"label":"5 樓"},{"isSynthetic":true,"provisional":true,"id":"district-01-f6","buildingId":"district-01","level":6,"label":"6 樓"},{"isSynthetic":true,"provisional":true,"id":"district-01-f7","buildingId":"district-01","level":7,"label":"7 樓"},{"isSynthetic":true,"provisional":true,"id":"district-01-f8","buildingId":"district-01","level":8,"label":"8 樓"},{"isSynthetic":true,"provisional":true,"id":"district-01-f9","buildingId":"district-01","level":9,"label":"9 樓"},{"isSynthetic":true,"provisional":true,"id":"district-01-f10","buildingId":"district-01","level":10,"label":"10 樓"},{"isSynthetic":true,"provisional":true,"id":"district-02-f1","buildingId":"district-02","level":1,"label":"1 樓"},{"isSynthetic":true,"provisional":true,"id":"district-02-f2","buildingId":"district-02","level":2,"label":"2 樓"},{"isSynthetic":true,"provisional":true,"id":"district-02-f3","buildingId":"district-02","level":3,"label":"3 樓"},{"isSynthetic":true,"provisional":true,"id":"district-02-f4","buildingId":"district-02","level":4,"label":"4 樓"},{"isSynthetic":true,"provisional":true,"id":"district-02-f5","buildingId":"district-02","level":5,"label":"5 樓"},{"isSynthetic":true,"provisional":true,"id":"district-02-f6","buildingId":"district-02","level":6,"label":"6 樓"},{"isSynthetic":true,"provisional":true,"id":"district-02-f7","buildingId":"district-02","level":7,"label":"7 樓"},{"isSynthetic":true,"provisional":true,"id":"district-03-f1","buildingId":"district-03","level":1,"label":"1 樓"},{"isSynthetic":true,"provisional":true,"id":"district-03-f2","buildingId":"district-03","level":2,"label":"2 樓"},{"isSynthetic":true,"provisional":true,"id":"district-03-f3","buildingId":"district-03","level":3,"label":"3 樓"},{"isSynthetic":true,"provisional":true,"id":"district-03-f4","buildingId":"district-03","level":4,"label":"4 樓"},{"isSynthetic":true,"provisional":true,"id":"district-03-f5","buildingId":"district-03","level":5,"label":"5 樓"},{"isSynthetic":true,"provisional":true,"id":"district-03-f6","buildingId":"district-03","level":6,"label":"6 樓"},{"isSynthetic":true,"provisional":true,"id":"district-03-f7","buildingId":"district-03","level":7,"label":"7 樓"},{"isSynthetic":true,"provisional":true,"id":"district-03-f8","buildingId":"district-03","level":8,"label":"8 樓"},{"isSynthetic":true,"provisional":true,"id":"district-03-f9","buildingId":"district-03","level":9,"label":"9 樓"},{"isSynthetic":true,"provisional":true,"id":"district-03-f10","buildingId":"district-03","level":10,"label":"10 樓"},{"isSynthetic":true,"provisional":true,"id":"district-03-f11","buildingId":"district-03","level":11,"label":"11 樓"},{"isSynthetic":true,"provisional":true,"id":"district-03-f12","buildingId":"district-03","level":12,"label":"12 樓"},{"isSynthetic":true,"provisional":true,"id":"district-04-f1","buildingId":"district-04","level":1,"label":"1 樓"},{"isSynthetic":true,"provisional":true,"id":"district-04-f2","buildingId":"district-04","level":2,"label":"2 樓"},{"isSynthetic":true,"provisional":true,"id":"district-04-f3","buildingId":"district-04","level":3,"label":"3 樓"},{"isSynthetic":true,"provisional":true,"id":"district-04-f4","buildingId":"district-04","level":4,"label":"4 樓"},{"isSynthetic":true,"provisional":true,"id":"district-04-f5","buildingId":"district-04","level":5,"label":"5 樓"},{"isSynthetic":true,"provisional":true,"id":"district-05-f1","buildingId":"district-05","level":1,"label":"1 樓"},{"isSynthetic":true,"provisional":true,"id":"district-05-f2","buildingId":"district-05","level":2,"label":"2 樓"},{"isSynthetic":true,"provisional":true,"id":"district-05-f3","buildingId":"district-05","level":3,"label":"3 樓"},{"isSynthetic":true,"provisional":true,"id":"district-05-f4","buildingId":"district-05","level":4,"label":"4 樓"},{"isSynthetic":true,"provisional":true,"id":"district-05-f5","buildingId":"district-05","level":5,"label":"5 樓"},{"isSynthetic":true,"provisional":true,"id":"district-05-f6","buildingId":"district-05","level":6,"label":"6 樓"},{"isSynthetic":true,"provisional":true,"id":"district-05-f7","buildingId":"district-05","level":7,"label":"7 樓"},{"isSynthetic":true,"provisional":true,"id":"district-05-f8","buildingId":"district-05","level":8,"label":"8 樓"},{"isSynthetic":true,"provisional":true,"id":"district-05-f9","buildingId":"district-05","level":9,"label":"9 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f1","buildingId":"district-07","level":1,"label":"1 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f2","buildingId":"district-07","level":2,"label":"2 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f3","buildingId":"district-07","level":3,"label":"3 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f4","buildingId":"district-07","level":4,"label":"4 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f5","buildingId":"district-07","level":5,"label":"5 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f6","buildingId":"district-07","level":6,"label":"6 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f7","buildingId":"district-07","level":7,"label":"7 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f8","buildingId":"district-07","level":8,"label":"8 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f9","buildingId":"district-07","level":9,"label":"9 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f10","buildingId":"district-07","level":10,"label":"10 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f11","buildingId":"district-07","level":11,"label":"11 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f12","buildingId":"district-07","level":12,"label":"12 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f13","buildingId":"district-07","level":13,"label":"13 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f14","buildingId":"district-07","level":14,"label":"14 樓"},{"isSynthetic":true,"provisional":true,"id":"district-08-f1","buildingId":"district-08","level":1,"label":"1 樓"},{"isSynthetic":true,"provisional":true,"id":"district-08-f2","buildingId":"district-08","level":2,"label":"2 樓"},{"isSynthetic":true,"provisional":true,"id":"district-08-f3","buildingId":"district-08","level":3,"label":"3 樓"},{"isSynthetic":true,"provisional":true,"id":"district-08-f4","buildingId":"district-08","level":4,"label":"4 樓"},{"isSynthetic":true,"provisional":true,"id":"district-08-f5","buildingId":"district-08","level":5,"label":"5 樓"},{"isSynthetic":true,"provisional":true,"id":"district-08-f6","buildingId":"district-08","level":6,"label":"6 樓"},{"isSynthetic":true,"provisional":true,"id":"district-09-f1","buildingId":"district-09","level":1,"label":"1 樓"},{"isSynthetic":true,"provisional":true,"id":"district-09-f2","buildingId":"district-09","level":2,"label":"2 樓"},{"isSynthetic":true,"provisional":true,"id":"district-09-f3","buildingId":"district-09","level":3,"label":"3 樓"},{"isSynthetic":true,"provisional":true,"id":"district-09-f4","buildingId":"district-09","level":4,"label":"4 樓"},{"isSynthetic":true,"provisional":true,"id":"district-09-f5","buildingId":"district-09","level":5,"label":"5 樓"},{"isSynthetic":true,"provisional":true,"id":"district-09-f6","buildingId":"district-09","level":6,"label":"6 樓"},{"isSynthetic":true,"provisional":true,"id":"district-09-f7","buildingId":"district-09","level":7,"label":"7 樓"},{"isSynthetic":true,"provisional":true,"id":"district-09-f8","buildingId":"district-09","level":8,"label":"8 樓"},{"isSynthetic":true,"provisional":true,"id":"district-10-f1","buildingId":"district-10","level":1,"label":"1 樓"},{"isSynthetic":true,"provisional":true,"id":"district-10-f2","buildingId":"district-10","level":2,"label":"2 樓"},{"isSynthetic":true,"provisional":true,"id":"district-10-f3","buildingId":"district-10","level":3,"label":"3 樓"},{"isSynthetic":true,"provisional":true,"id":"district-10-f4","buildingId":"district-10","level":4,"label":"4 樓"},{"isSynthetic":true,"provisional":true,"id":"district-11-f1","buildingId":"district-11","level":1,"label":"1 樓"},{"isSynthetic":true,"provisional":true,"id":"district-11-f2","buildingId":"district-11","level":2,"label":"2 樓"},{"isSynthetic":true,"provisional":true,"id":"district-11-f3","buildingId":"district-11","level":3,"label":"3 樓"},{"isSynthetic":true,"provisional":true,"id":"district-11-f4","buildingId":"district-11","level":4,"label":"4 樓"},{"isSynthetic":true,"provisional":true,"id":"district-11-f5","buildingId":"district-11","level":5,"label":"5 樓"},{"isSynthetic":true,"provisional":true,"id":"district-11-f6","buildingId":"district-11","level":6,"label":"6 樓"},{"isSynthetic":true,"provisional":true,"id":"district-11-f7","buildingId":"district-11","level":7,"label":"7 樓"},{"isSynthetic":true,"provisional":true,"id":"district-11-f8","buildingId":"district-11","level":8,"label":"8 樓"},{"isSynthetic":true,"provisional":true,"id":"district-11-f9","buildingId":"district-11","level":9,"label":"9 樓"},{"isSynthetic":true,"provisional":true,"id":"district-11-f10","buildingId":"district-11","level":10,"label":"10 樓"},{"isSynthetic":true,"provisional":true,"id":"district-11-f11","buildingId":"district-11","level":11,"label":"11 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f1","buildingId":"district-13","level":1,"label":"1 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f2","buildingId":"district-13","level":2,"label":"2 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f3","buildingId":"district-13","level":3,"label":"3 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f4","buildingId":"district-13","level":4,"label":"4 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f5","buildingId":"district-13","level":5,"label":"5 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f6","buildingId":"district-13","level":6,"label":"6 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f7","buildingId":"district-13","level":7,"label":"7 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f8","buildingId":"district-13","level":8,"label":"8 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f9","buildingId":"district-13","level":9,"label":"9 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f10","buildingId":"district-13","level":10,"label":"10 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f11","buildingId":"district-13","level":11,"label":"11 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f12","buildingId":"district-13","level":12,"label":"12 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f13","buildingI</x:v>
+        <x:v>{"schemaVersion":"0.1-demo","isSynthetic":true,"notice":"全區合成演示：20 個大廈位置用作介面測試；樓名、地址、樓層、單位、住戶及記錄均屬虛構，不代表地圖底圖中的真實建築或居民。依原紙本＋Excel 工作流設計，欄位仍待機構確認。","buildings":[{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an","name":"裕安樓","address":"西營盤示範街 1 號","layoutDeclared":true,"floorCount":8,"initialCoverage":"UNVISITED","coordinates":{"lng":114.14178818464279,"lat":22.286363930711317},"footprint":[[114.14168894290924,22.286500432351488],[114.1418981552124,22.286495468660235],[114.14189279079437,22.286227429071147],[114.14167821407318,22.286237356472498],[114.14168894290924,22.286500432351488]]},{"isSynthetic":true,"provisional":true,"id":"bldg-hoi-king","name":"海景樓","address":"西營盤示範街 8 號","layoutDeclared":true,"floorCount":2,"initialCoverage":"UNVISITED","coordinates":{"lng":114.14255797863007,"lat":22.28661211534631},"footprint":[[114.14262235164642,22.286664234063778],[114.14262235164642,22.286619560888553],[114.14259016513824,22.286624524575387],[114.14258480072021,22.286589778763798],[114.14263308048248,22.286589778763798],[114.14263308048248,22.286555032943582],[114.14248287677765,22.286559996632704],[114.14248287677765,22.28659474245171],[114.14253115653992,22.28659474245171],[114.14253115653992,22.286624524575387],[114.14249897003174,22.286624524575387],[114.14249897003174,22.286669197749035],[114.14262235164642,22.286664234063778]]},{"isSynthetic":true,"provisional":true,"id":"bldg-duk-cheong","name":"德昌樓","address":"西營盤示範街 16 號","layoutDeclared":false,"initialCoverage":"UNKNOWN","coordinates":{"lng":114.14136976003647,"lat":22.286808180844794},"footprint":[[114.1414475440979,22.286733725641312],[114.14129197597504,22.286733725641312],[114.14129197597504,22.286882636048276],[114.1414475440979,22.286877672370593],[114.1414475440979,22.286733725641312]]},{"isSynthetic":true,"provisional":true,"id":"bldg-on-wo","name":"安和樓","address":"西營盤示範街 24 號","layoutDeclared":false,"initialCoverage":"UNKNOWN","coordinates":{"lng":114.14208590984344,"lat":22.28576580411479},"footprint":[[114.14213418960571,22.285825368723906],[114.14212882518768,22.28570127579063],[114.14203763008118,22.285706239510063],[114.1420429944992,22.285830332438948],[114.14213418960571,22.285825368723906]]},{"isSynthetic":true,"provisional":true,"id":"district-01","name":"晴里樓","address":"演示街區 01 號 · 虛構地址","coordinates":{"lng":114.13954049348831,"lat":22.287835658837054},"footprint":[[114.13945734500885,22.287890258967195],[114.13946807384491,22.287865440755937],[114.13947880268097,22.28787040439856],[114.13946270942688,22.287920040814882],[114.1395378112793,22.287939895376482],[114.13955390453339,22.287890258967195],[114.13956463336945,22.287890258967195],[114.13954854011536,22.287944859016434],[114.13962364196777,22.28796471357451],[114.13963973522186,22.287910113533016],[114.13965582847595,22.28791507717405],[114.13966655731201,22.28787536804097],[114.13965046405792,22.28787040439856],[114.13966119289398,22.287835658896626],[114.1396826505661,22.287840622540287],[114.13970410823822,22.28778105880474],[114.13943588733673,22.287706604099597],[114.1393768787384,22.28789522260891],[114.13945198059082,22.28791507717405],[114.13945734500885,22.287890258967195]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":10},{"isSynthetic":true,"provisional":true,"id":"district-02","name":"青禾樓","address":"演示街區 02 號 · 虛構地址","coordinates":{"lng":114.14060264825821,"lat":22.287644558357755},"footprint":[[114.14048731327057,22.28780091338608],[114.14061069488525,22.28783069525278],[114.14062678813934,22.28778105880474],[114.1406911611557,22.287795949740996],[114.14071798324585,22.287696676802582],[114.14065897464752,22.28768178585574],[114.14071261882782,22.28749316705843],[114.1405838727951,22.28745842146273],[114.14048731327057,22.28780091338608]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":7},{"isSynthetic":true,"provisional":true,"id":"district-03","name":"映榕樓","address":"演示街區 03 號 · 虛構地址","coordinates":{"lng":114.14200276136398,"lat":22.287753758732258},"footprint":[[114.14189279079437,22.287686749504857],[114.1418981552124,22.287825731608777],[114.1421127319336,22.28782076796459],[114.14210736751556,22.28768178585574],[114.14189279079437,22.287686749504857]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":12},{"isSynthetic":true,"provisional":true,"id":"district-04","name":"小滿樓","address":"演示街區 04 號 · 虛構地址","coordinates":{"lng":114.14324462413788,"lat":22.287714049553372},"footprint":[[114.14331436157227,22.28778105880474],[114.14330899715424,22.28764207665641],[114.14319097995758,22.287647040306936],[114.14319097995758,22.287751276927438],[114.14317488670349,22.287751276927438],[114.14317488670349,22.287786022450334],[114.14331436157227,22.28778105880474]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":5},{"isSynthetic":true,"provisional":true,"id":"district-05","name":"常悅樓","address":"演示街區 05 號 · 虛構地址","coordinates":{"lng":114.13936883211136,"lat":22.286842926596464},"footprint":[[114.13924276828766,22.28687270869274],[114.13945734500885,22.286927309139443],[114.13949489593506,22.286818108224736],[114.13928031921387,22.286758544053484],[114.13924276828766,22.28687270869274]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":9},{"isSynthetic":true,"provisional":true,"id":"district-06","name":"知秋樓","address":"演示街區 06 號 · 虛構地址","coordinates":{"lng":114.14092719554901,"lat":22.286840444772693},"footprint":[[114.14082527160645,22.28683796294284],[114.14087355136871,22.28683796294284],[114.14087355136871,22.2868925634031],[114.14098620414734,22.286887599725773],[114.14098620414734,22.28683299926358],[114.14102911949158,22.28683299926358],[114.14102911949158,22.286788326142286],[114.14082527160645,22.286793289823123],[114.14082527160645,22.28683796294284]],"layoutDeclared":false,"initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-07","name":"晴川樓","address":"演示街區 07 號 · 虛構地址","coordinates":{"lng":114.14216101169586,"lat":22.286723798239954},"footprint":[[114.14209127426147,22.286624524575387],[114.14209127426147,22.28665430669274],[114.14210200309753,22.28665430669274],[114.14210736751556,22.286793289823123],[114.1420966386795,22.286793289823123],[114.1420966386795,22.28682307190452],[114.14218246936798,22.28682307190452],[114.14217174053192,22.286763507735387],[114.14223074913025,22.286763507735387],[114.14223074913025,22.286674161434107],[114.14217174053192,22.286674161434107],[114.14217710494995,22.286624524575387],[114.14209127426147,22.286624524575387]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":14},{"isSynthetic":true,"provisional":true,"id":"district-08","name":"穗安樓","address":"演示街區 08 號 · 虛構地址","coordinates":{"lng":114.14348870515823,"lat":22.286728761932885},"footprint":[[114.14357721805573,22.286644379321004],[114.14339482784271,22.286649343006957],[114.14340019226074,22.286813144544766],[114.14358258247375,22.286808180864625],[114.14357721805573,22.286644379321004]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":6},{"isSynthetic":true,"provisional":true,"id":"district-09","name":"棠和樓","address":"演示街區 09 號 · 虛構地址","coordinates":{"lng":114.13955926895142,"lat":22.28589237884831},"footprint":[[114.13951098918915,22.28595442525767],[114.13961291313171,22.28594449783624],[114.13961291313171,22.28592960670275],[114.13965046405792,22.285924642991233],[114.13964509963989,22.285879969579653],[114.13960754871368,22.28588493329275],[114.13960218429565,22.285830332438948],[114.13955926895142,22.28583529615382],[114.13956463336945,22.285870042152922],[114.13954317569733,22.285870042152922],[114.13954317569733,22.28583529615382],[114.13950026035309,22.285840259868493],[114.13950562477112,22.285894860718443],[114.13946807384491,22.285894860718443],[114.13947343826294,22.285939534125234],[114.13951098918915,22.285939534125234],[114.13951098918915,22.28595442525767]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":8},{"isSynthetic":true,"provisional":true,"id":"district-10","name":"日和樓","address":"演示街區 10 號 · 虛構地址","coordinates":{"lng":114.14058923721313,"lat":22.285837777977676},"footprint":[[114.1406375169754,22.285899824431013],[114.14064824581146,22.285899824431013],[114.14064288139343,22.28576580412968],[114.1406375169754,22.28576580412968],[114.14063215255737,22.285740985541267],[114.14057850837708,22.285745949259294],[114.14057850837708,22.285775731563803],[114.14056777954102,22.285775731563803],[114.14056241512299,22.285800550146064],[114.14053022861481,22.285800550146064],[114.14053022861481,22.285855151011503],[114.1405463218689,22.285855151011503],[114.1405463218689,22.285875005866373],[114.14053022861481,22.285875005866373],[114.14053559303284,22.285924642991233],[114.14062142372131,22.285934570414085],[114.14062142372131,22.28592960670275],[114.1406375169754,22.28592960670275],[114.1406375169754,22.285899824431013]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":4},{"isSynthetic":true,"provisional":true,"id":"district-11","name":"朗月樓","address":"演示街區 11 號 · 虛構地址","coordinates":{"lng":114.14172112941742,"lat":22.285909751848486},"footprint":[[114.14187133312225,22.2858650784393],[114.14156556129456,22.285875005866373],[114.14156556129456,22.28595442525767],[114.14187669754028,22.28594449783624],[114.14187133312225,22.2858650784393]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":11},{"isSynthetic":true,"provisional":true,"id":"district-12","name":"杏林樓","address":"演示街區 12 號 · 虛構地址","coordinates":{"lng":114.14298176765442,"lat":22.285726094375427},"footprint":[[114.14291203022003,22.28575091297715],[114.14291203022003,22.285780695280607],[114.14305686950684,22.285775731563803],[114.14305686950684,22.285671493470247],[114.142906665802,22.28567645719076],[114.14291203022003,22.28575091297715]],"layoutDeclared":false,"initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"district-13","name":"拾光樓","address":"演示街區 13 號 · 虛構地址","coordinates":{"lng":114.13944393396378,"lat":22.284753202106018},"footprint":[[114.13941442966461,22.284693637093838],[114.13939833641052,22.284693637093838],[114.13935005664825,22.284668818315083],[114.13934469223022,22.284678745827122],[114.13930177688599,22.28465392704571],[114.13926959037781,22.2847184558682],[114.13938224315643,22.284768093403684],[114.13938760757446,22.284852477173544],[114.13942515850067,22.284847513423784],[114.13942515850067,22.284857440923133],[114.13946807384491,22.284857440923133],[114.13946270942688,22.284847513423784],[114.13950026035309,22.284842549673854],[114.13949489593506,22.284768093403684],[114.13961827754974,22.284698600849055],[114.13958609104156,22.2846489632889],[114.13954317569733,22.284668818315083],[114.1395378112793,22.284658890802348],[114.13947880268097,22.284688673338437],[114.13946270942688,22.284693637093838],[114.13946270942688,22.284673782071195],[114.13940906524658,22.284673782071195],[114.13941442966461,22.284693637093838]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":13},{"isSynthetic":true,"provisional":true,"id":"district-14","name":"和煦樓","address":"演示街區 14 號 · 虛構地址","coordinates":{"lng":114.14081990718842,"lat":22.284790430151403},"footprint":[[114.14072871208191,22.284604289469698],[114.14073944091797,22.28498649835042],[114.14082527160645,22.284981534605436],[114.14082527160645,22.28496664336936],[114.14091110229492,22.28496664336936],[114.14090037345886,22.284594361952387],[114.14087355136871,22.284594361952387],[114.14087355136871,22.284604289469698],[114.14072871208191,22.284604289469698]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":6},{"isSynthetic":true,"provisional":true,"id":"district-15","name":"榕溪樓","address":"演示街區 15 號 · 虛構地址","coordinates":{"lng":114.1420429944992,"lat":22.284894669027736},"footprint":[[114.14195716381073,22.284951752131732],[114.14212882518768,22.284946788385483],[114.14212346076965,22.28483758592374],[114.142005443573,22.28483758592374],[114.142005443573,22.284877295919713],[114.14195716381073,22.284882259668407],[114.14195716381073,22.284951752131732]],"layoutDeclared":true,"initialCoverage":"UNVISITED","floorCount":8},{"isSynthetic":true,"provisional":true,"id":"district-16","name":"微光樓","address":"演示街區 16 號 · 虛構地址","coordinates":{"lng":114.14333045482635,"lat":22.284941824574837},"footprint":[[114.14327681064606,22.285075845730304],[114.14339482784271,22.285070881988474],[114.14337873458862,22.28480780341937],[114.14326608181,22.284812767170536],[114.14327681064606,22.285075845730304]],"layoutDeclared":false,"initialCoverage":"UNKNOWN"}],"floors":[{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f1","buildingId":"bldg-yu-an","label":"1F","level":1},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f2","buildingId":"bldg-yu-an","label":"2F","level":2},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f3","buildingId":"bldg-yu-an","label":"3F","level":3},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f4","buildingId":"bldg-yu-an","label":"4F","level":4},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f5","buildingId":"bldg-yu-an","label":"5F","level":5},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f6","buildingId":"bldg-yu-an","label":"6F","level":6},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f7","buildingId":"bldg-yu-an","label":"7F","level":7},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f8","buildingId":"bldg-yu-an","label":"8F","level":8},{"isSynthetic":true,"provisional":true,"id":"bldg-hoi-king-f1","buildingId":"bldg-hoi-king","label":"1F","level":1},{"isSynthetic":true,"provisional":true,"id":"bldg-hoi-king-f2","buildingId":"bldg-hoi-king","label":"2F","level":2},{"isSynthetic":true,"provisional":true,"id":"district-01-f1","buildingId":"district-01","level":1,"label":"1 樓"},{"isSynthetic":true,"provisional":true,"id":"district-01-f2","buildingId":"district-01","level":2,"label":"2 樓"},{"isSynthetic":true,"provisional":true,"id":"district-01-f3","buildingId":"district-01","level":3,"label":"3 樓"},{"isSynthetic":true,"provisional":true,"id":"district-01-f4","buildingId":"district-01","level":4,"label":"4 樓"},{"isSynthetic":true,"provisional":true,"id":"district-01-f5","buildingId":"district-01","level":5,"label":"5 樓"},{"isSynthetic":true,"provisional":true,"id":"district-01-f6","buildingId":"district-01","level":6,"label":"6 樓"},{"isSynthetic":true,"provisional":true,"id":"district-01-f7","buildingId":"district-01","level":7,"label":"7 樓"},{"isSynthetic":true,"provisional":true,"id":"district-01-f8","buildingId":"district-01","level":8,"label":"8 樓"},{"isSynthetic":true,"provisional":true,"id":"district-01-f9","buildingId":"district-01","level":9,"label":"9 樓"},{"isSynthetic":true,"provisional":true,"id":"district-01-f10","buildingId":"district-01","level":10,"label":"10 樓"},{"isSynthetic":true,"provisional":true,"id":"district-02-f1","buildingId":"district-02","level":1,"label":"1 樓"},{"isSynthetic":true,"provisional":true,"id":"district-02-f2","buildingId":"district-02","level":2,"label":"2 樓"},{"isSynthetic":true,"provisional":true,"id":"district-02-f3","buildingId":"district-02","level":3,"label":"3 樓"},{"isSynthetic":true,"provisional":true,"id":"district-02-f4","buildingId":"district-02","level":4,"label":"4 樓"},{"isSynthetic":true,"provisional":true,"id":"district-02-f5","buildingId":"district-02","level":5,"label":"5 樓"},{"isSynthetic":true,"provisional":true,"id":"district-02-f6","buildingId":"district-02","level":6,"label":"6 樓"},{"isSynthetic":true,"provisional":true,"id":"district-02-f7","buildingId":"district-02","level":7,"label":"7 樓"},{"isSynthetic":true,"provisional":true,"id":"district-03-f1","buildingId":"district-03","level":1,"label":"1 樓"},{"isSynthetic":true,"provisional":true,"id":"district-03-f2","buildingId":"district-03","level":2,"label":"2 樓"},{"isSynthetic":true,"provisional":true,"id":"district-03-f3","buildingId":"district-03","level":3,"label":"3 樓"},{"isSynthetic":true,"provisional":true,"id":"district-03-f4","buildingId":"district-03","level":4,"label":"4 樓"},{"isSynthetic":true,"provisional":true,"id":"district-03-f5","buildingId":"district-03","level":5,"label":"5 樓"},{"isSynthetic":true,"provisional":true,"id":"district-03-f6","buildingId":"district-03","level":6,"label":"6 樓"},{"isSynthetic":true,"provisional":true,"id":"district-03-f7","buildingId":"district-03","level":7,"label":"7 樓"},{"isSynthetic":true,"provisional":true,"id":"district-03-f8","buildingId":"district-03","level":8,"label":"8 樓"},{"isSynthetic":true,"provisional":true,"id":"district-03-f9","buildingId":"district-03","level":9,"label":"9 樓"},{"isSynthetic":true,"provisional":true,"id":"district-03-f10","buildingId":"district-03","level":10,"label":"10 樓"},{"isSynthetic":true,"provisional":true,"id":"district-03-f11","buildingId":"district-03","level":11,"label":"11 樓"},{"isSynthetic":true,"provisional":true,"id":"district-03-f12","buildingId":"district-03","level":12,"label":"12 樓"},{"isSynthetic":true,"provisional":true,"id":"district-04-f1","buildingId":"district-04","level":1,"label":"1 樓"},{"isSynthetic":true,"provisional":true,"id":"district-04-f2","buildingId":"district-04","level":2,"label":"2 樓"},{"isSynthetic":true,"provisional":true,"id":"district-04-f3","buildingId":"district-04","level":3,"label":"3 樓"},{"isSynthetic":true,"provisional":true,"id":"district-04-f4","buildingId":"district-04","level":4,"label":"4 樓"},{"isSynthetic":true,"provisional":true,"id":"district-04-f5","buildingId":"district-04","level":5,"label":"5 樓"},{"isSynthetic":true,"provisional":true,"id":"district-05-f1","buildingId":"district-05","level":1,"label":"1 樓"},{"isSynthetic":true,"provisional":true,"id":"district-05-f2","buildingId":"district-05","level":2,"label":"2 樓"},{"isSynthetic":true,"provisional":true,"id":"district-05-f3","buildingId":"district-05","level":3,"label":"3 樓"},{"isSynthetic":true,"provisional":true,"id":"district-05-f4","buildingId":"district-05","level":4,"label":"4 樓"},{"isSynthetic":true,"provisional":true,"id":"district-05-f5","buildingId":"district-05","level":5,"label":"5 樓"},{"isSynthetic":true,"provisional":true,"id":"district-05-f6","buildingId":"district-05","level":6,"label":"6 樓"},{"isSynthetic":true,"provisional":true,"id":"district-05-f7","buildingId":"district-05","level":7,"label":"7 樓"},{"isSynthetic":true,"provisional":true,"id":"district-05-f8","buildingId":"district-05","level":8,"label":"8 樓"},{"isSynthetic":true,"provisional":true,"id":"district-05-f9","buildingId":"district-05","level":9,"label":"9 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f1","buildingId":"district-07","level":1,"label":"1 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f2","buildingId":"district-07","level":2,"label":"2 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f3","buildingId":"district-07","level":3,"label":"3 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f4","buildingId":"district-07","level":4,"label":"4 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f5","buildingId":"district-07","level":5,"label":"5 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f6","buildingId":"district-07","level":6,"label":"6 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f7","buildingId":"district-07","level":7,"label":"7 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f8","buildingId":"district-07","level":8,"label":"8 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f9","buildingId":"district-07","level":9,"label":"9 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f10","buildingId":"district-07","level":10,"label":"10 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f11","buildingId":"district-07","level":11,"label":"11 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f12","buildingId":"district-07","level":12,"label":"12 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f13","buildingId":"district-07","level":13,"label":"13 樓"},{"isSynthetic":true,"provisional":true,"id":"district-07-f14","buildingId":"district-07","level":14,"label":"14 樓"},{"isSynthetic":true,"provisional":true,"id":"district-08-f1","buildingId":"district-08","level":1,"label":"1 樓"},{"isSynthetic":true,"provisional":true,"id":"district-08-f2","buildingId":"district-08","level":2,"label":"2 樓"},{"isSynthetic":true,"provisional":true,"id":"district-08-f3","buildingId":"district-08","level":3,"label":"3 樓"},{"isSynthetic":true,"provisional":true,"id":"district-08-f4","buildingId":"district-08","level":4,"label":"4 樓"},{"isSynthetic":true,"provisional":true,"id":"district-08-f5","buildingId":"district-08","level":5,"label":"5 樓"},{"isSynthetic":true,"provisional":true,"id":"district-08-f6","buildingId":"district-08","level":6,"label":"6 樓"},{"isSynthetic":true,"provisional":true,"id":"district-09-f1","buildingId":"district-09","level":1,"label":"1 樓"},{"isSynthetic":true,"provisional":true,"id":"district-09-f2","buildingId":"district-09","level":2,"label":"2 樓"},{"isSynthetic":true,"provisional":true,"id":"district-09-f3","buildingId":"district-09","level":3,"label":"3 樓"},{"isSynthetic":true,"provisional":true,"id":"district-09-f4","buildingId":"district-09","level":4,"label":"4 樓"},{"isSynthetic":true,"provisional":true,"id":"district-09-f5","buildingId":"district-09","level":5,"label":"5 樓"},{"isSynthetic":true,"provisional":true,"id":"district-09-f6","buildingId":"district-09","level":6,"label":"6 樓"},{"isSynthetic":true,"provisional":true,"id":"district-09-f7","buildingId":"district-09","level":7,"label":"7 樓"},{"isSynthetic":true,"provisional":true,"id":"district-09-f8","buildingId":"district-09","level":8,"label":"8 樓"},{"isSynthetic":true,"provisional":true,"id":"district-10-f1","buildingId":"district-10","level":1,"label":"1 樓"},{"isSynthetic":true,"provisional":true,"id":"district-10-f2","buildingId":"district-10","level":2,"label":"2 樓"},{"isSynthetic":true,"provisional":true,"id":"district-10-f3","buildingId":"district-10","level":3,"label":"3 樓"},{"isSynthetic":true,"provisional":true,"id":"district-10-f4","buildingId":"district-10","level":4,"label":"4 樓"},{"isSynthetic":true,"provisional":true,"id":"district-11-f1","buildingId":"district-11","level":1,"label":"1 樓"},{"isSynthetic":true,"provisional":true,"id":"district-11-f2","buildingId":"district-11","level":2,"label":"2 樓"},{"isSynthetic":true,"provisional":true,"id":"district-11-f3","buildingId":"district-11","level":3,"label":"3 樓"},{"isSynthetic":true,"provisional":true,"id":"district-11-f4","buildingId":"district-11","level":4,"label":"4 樓"},{"isSynthetic":true,"provisional":true,"id":"district-11-f5","buildingId":"district-11","level":5,"label":"5 樓"},{"isSynthetic":true,"provisional":true,"id":"district-11-f6","buildingId":"district-11","level":6,"label":"6 樓"},{"isSynthetic":true,"provisional":true,"id":"district-11-f7","buildingId":"district-11","level":7,"label":"7 樓"},{"isSynthetic":true,"provisional":true,"id":"district-11-f8","buildingId":"district-11","level":8,"label":"8 樓"},{"isSynthetic":true,"provisional":true,"id":"district-11-f9","buildingId":"district-11","level":9,"label":"9 樓"},{"isSynthetic":true,"provisional":true,"id":"district-11-f10","buildingId":"district-11","level":10,"label":"10 樓"},{"isSynthetic":true,"provisional":true,"id":"district-11-f11","buildingId":"district-11","level":11,"label":"11 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f1","buildingId":"district-13","level":1,"label":"1 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f2","buildingId":"district-13","level":2,"label":"2 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f3","buildingId":"district-13","level":3,"label":"3 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f4","buildingId":"district-13","level":4,"label":"4 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f5","buildingId":"district-13","level":5,"label":"5 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f6","buildingId":"district-13","level":6,"label":"6 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f7","buildingId":"district-13","level":7,"label":"7 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f8","buildingId":"district-13","level":8,"label":"8 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f9","buildingId":"district-13","level":9,"label":"9 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f10","buildingId":"district-13","level":10,"label":"10 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f11","buildingId":"district-13","level":11,"label":"11 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f12","buildingId":"district-13","level":12,"label":"12 樓"},{"isSynthetic":true,"provisional":true,"id":"district-13-f13","buildingI</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="25" customHeight="1">
